--- a/dataset_making/master.xlsx
+++ b/dataset_making/master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,143 +456,143 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>release_method</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>last5_steps_frame</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>last5_step_intervals_s</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>step_duration_mean_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>step_duration_std_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>step_duration_cv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>final5_total_duration_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>stride_duration_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>stride_length_m</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>bfc_frame</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ffc_frame</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arm_back_frame</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>release_frame.1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>elbow_angle_arm_back_deg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>elbow_angle_release_deg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elbow_extension_deg</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>knee_angle_ffc_deg</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>knee_angle_release_deg</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>head_dx_ffc_cm</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>head_dy_ffc_cm</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>head_d_ffc_cm</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>head_dx_bfc_cm</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>head_dy_bfc_cm</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>head_d_bfc_cm</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>peak_wrist_speed_m_s</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>wrist_speed_at_release_m_s</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>release_method</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B-04_T-04</t>
+          <t>B-01_T-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.97357992073976</v>
+        <v>59.97322623828648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -605,97 +605,101 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>407</v>
+        <v>181</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[338, 361, 370, 392, 405]</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.3835022026431718, 0.1500660792951542, 0.3668281938325991, 0.21676211453744496]</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.2792896475770925</v>
+          <t>[86, 108, 127, 163, 174]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[0.36683035714285717, 0.31680803571428573, 0.6002678571428571, 0.18341517857142858]</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>0.0989086405495863</v>
+        <v>0.3668303571428572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.354143597543423</v>
+        <v>0.1505294213582035</v>
       </c>
       <c r="K2" t="n">
-        <v>1.11715859030837</v>
+        <v>0.4103515928469952</v>
       </c>
       <c r="L2" t="n">
-        <v>0.216762114537445</v>
+        <v>1.467321428571428</v>
       </c>
       <c r="M2" t="n">
-        <v>1.403926389005173</v>
+        <v>0.1834151785714286</v>
       </c>
       <c r="N2" t="n">
-        <v>392</v>
+        <v>0.9874416733839388</v>
       </c>
       <c r="O2" t="n">
-        <v>405</v>
+        <v>163</v>
       </c>
       <c r="P2" t="n">
-        <v>395</v>
+        <v>174</v>
       </c>
       <c r="Q2" t="n">
-        <v>407</v>
+        <v>166</v>
       </c>
       <c r="R2" t="n">
-        <v>168.5858250875124</v>
+        <v>181</v>
       </c>
       <c r="S2" t="n">
-        <v>176.3970325861677</v>
+        <v>175.8123433432208</v>
       </c>
       <c r="T2" t="n">
-        <v>7.811207498655278</v>
+        <v>165.7149479572232</v>
       </c>
       <c r="U2" t="n">
-        <v>157.2518220857597</v>
+        <v>-10.0973953859976</v>
       </c>
       <c r="V2" t="n">
-        <v>167.1277247317284</v>
+        <v>154.2438782122022</v>
       </c>
       <c r="W2" t="n">
-        <v>-21.98749333350851</v>
+        <v>134.9968098014093</v>
       </c>
       <c r="X2" t="n">
-        <v>-138.8259210785127</v>
+        <v>-12.80324573103566</v>
       </c>
       <c r="Y2" t="n">
-        <v>140.5563453793123</v>
+        <v>-134.8827113073759</v>
       </c>
       <c r="Z2" t="n">
-        <v>-39.63609599757035</v>
+        <v>135.4889992245798</v>
       </c>
       <c r="AA2" t="n">
-        <v>-140.1769772087822</v>
+        <v>-51.83775993651789</v>
       </c>
       <c r="AB2" t="n">
-        <v>145.6729386170268</v>
+        <v>-131.309876001777</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.84942526225402</v>
+        <v>141.1716575337915</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.84942526225402</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>12.38378390800123</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>12.37740178354601</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B-01_T-01</t>
+          <t>B-01_T-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.96321275291233</v>
+        <v>59.98113800691606</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -708,101 +712,105 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[30, 48, 64, 93, 113]</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.3001840490797546, 0.26683026584867076, 0.48362985685071574, 0.33353783231083844]</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3460455010224949</v>
+          <t>[97, 109, 133, 151, 174]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[0.200062893081761, 0.400125786163522, 0.30009433962264154, 0.3834538784067086]</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>0.0828616663530362</v>
+        <v>0.3209342243186583</v>
       </c>
       <c r="J3" t="n">
-        <v>0.239453095353636</v>
+        <v>0.07941062605823181</v>
       </c>
       <c r="K3" t="n">
-        <v>1.384182004089979</v>
+        <v>0.2474358296526967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3335378323108384</v>
+        <v>1.283736897274633</v>
       </c>
       <c r="M3" t="n">
-        <v>1.006496194325286</v>
+        <v>0.3834538784067086</v>
       </c>
       <c r="N3" t="n">
-        <v>93</v>
+        <v>1.142821065595325</v>
       </c>
       <c r="O3" t="n">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="P3" t="n">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="Q3" t="n">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="R3" t="n">
-        <v>177.2521232537956</v>
+        <v>182</v>
       </c>
       <c r="S3" t="n">
-        <v>160.4885255879036</v>
+        <v>72.53609581180426</v>
       </c>
       <c r="T3" t="n">
-        <v>-16.76359766589198</v>
+        <v>69.79052422809175</v>
       </c>
       <c r="U3" t="n">
-        <v>148.334486355258</v>
+        <v>-2.745571583712504</v>
       </c>
       <c r="V3" t="n">
-        <v>148.334486355258</v>
+        <v>150.2654004250381</v>
       </c>
       <c r="W3" t="n">
-        <v>12.59984851325907</v>
+        <v>133.3561579951623</v>
       </c>
       <c r="X3" t="n">
-        <v>-125.268706801503</v>
+        <v>-4.53535340537529</v>
       </c>
       <c r="Y3" t="n">
-        <v>125.9007747644072</v>
+        <v>-134.7248363863054</v>
       </c>
       <c r="Z3" t="n">
-        <v>-34.82559723608275</v>
+        <v>134.8011534439836</v>
       </c>
       <c r="AA3" t="n">
-        <v>-134.4015430735559</v>
+        <v>36.2626855326865</v>
       </c>
       <c r="AB3" t="n">
-        <v>138.8401851172878</v>
+        <v>-119.2636536836556</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.13905842469188</v>
+        <v>124.6547289597048</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.02566930515619</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>27.37344026692472</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>26.18097555819477</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B-08_T-05</t>
+          <t>B-01_T-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.96621621621622</v>
+        <v>59.972985141828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -811,97 +819,101 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[148, 165, 182, 208, 214]</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.28349295774647887, 0.28349295774647887, 0.4335774647887324, 0.10005633802816902]</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2751549295774648</v>
+          <t>[39, 60, 74, 104, 111]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[0.35015765765765766, 0.23343843843843845, 0.5002252252252253, 0.11671921921921923]</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1182119514397836</v>
+        <v>0.3001351351351352</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4296196023866007</v>
+        <v>0.1419754771723819</v>
       </c>
       <c r="K4" t="n">
-        <v>1.100619718309859</v>
+        <v>0.4730385101646222</v>
       </c>
       <c r="L4" t="n">
-        <v>0.100056338028169</v>
+        <v>1.20054054054054</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6616609304160802</v>
+        <v>0.1167192192192192</v>
       </c>
       <c r="N4" t="n">
-        <v>208</v>
+        <v>0.9406203648276278</v>
       </c>
       <c r="O4" t="n">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="P4" t="n">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="Q4" t="n">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="R4" t="n">
-        <v>175.7955657474623</v>
+        <v>119</v>
       </c>
       <c r="S4" t="n">
-        <v>141.4246276881661</v>
+        <v>179.3692891433796</v>
       </c>
       <c r="T4" t="n">
-        <v>-34.37093805929629</v>
+        <v>168.8145672851986</v>
       </c>
       <c r="U4" t="n">
-        <v>171.5444928115582</v>
+        <v>-10.55472185818095</v>
       </c>
       <c r="V4" t="n">
-        <v>170.1951672617541</v>
+        <v>160.2502097471716</v>
       </c>
       <c r="W4" t="n">
-        <v>-16.93560705136522</v>
+        <v>147.7509820281874</v>
       </c>
       <c r="X4" t="n">
-        <v>-118.7252859357457</v>
+        <v>-8.508803805132303</v>
       </c>
       <c r="Y4" t="n">
-        <v>119.9270957987511</v>
+        <v>-139.445660389785</v>
       </c>
       <c r="Z4" t="n">
-        <v>-49.9552757039819</v>
+        <v>139.7050176040126</v>
       </c>
       <c r="AA4" t="n">
-        <v>-111.606472238251</v>
+        <v>-39.89240118567241</v>
       </c>
       <c r="AB4" t="n">
-        <v>122.2764663217265</v>
+        <v>-134.4937829467733</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.33431621042135</v>
+        <v>140.2853567685965</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.720696919545922</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>12.19491007457519</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>11.99231080687573</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B-05_T-10</t>
+          <t>B-07_T-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.97403721332756</v>
+        <v>59.98083679335676</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -914,101 +926,89 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[111, 136, 150, 173, 180]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[0.41684704184704185, 0.23343434343434344, 0.3834992784992785, 0.11671717171717172]</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2876244588744589</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1204536491799587</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.4187879210666634</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.150497835497835</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1167171717171717</v>
-      </c>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>1.139849683142038</v>
+        <v>0.1167039403620873</v>
       </c>
       <c r="N5" t="n">
-        <v>173</v>
+        <v>0.3423074091036046</v>
       </c>
       <c r="O5" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="Q5" t="n">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="R5" t="n">
-        <v>172.7424337572813</v>
+        <v>230</v>
       </c>
       <c r="S5" t="n">
-        <v>169.2593351252305</v>
+        <v>179.2654528840065</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.483098632050769</v>
+        <v>166.7339224089391</v>
       </c>
       <c r="U5" t="n">
-        <v>179.076376492534</v>
+        <v>-12.53153047506734</v>
       </c>
       <c r="V5" t="n">
-        <v>176.9867854932333</v>
+        <v>72.11780083079137</v>
       </c>
       <c r="W5" t="n">
-        <v>-10.20855204500593</v>
+        <v>167.7296439716362</v>
       </c>
       <c r="X5" t="n">
-        <v>-161.2637897063322</v>
+        <v>-1.001252233836396</v>
       </c>
       <c r="Y5" t="n">
-        <v>161.5865848556238</v>
+        <v>-101.7769831467103</v>
       </c>
       <c r="Z5" t="n">
-        <v>-42.45373930637093</v>
+        <v>101.7819080410734</v>
       </c>
       <c r="AA5" t="n">
-        <v>-162.0276114385457</v>
+        <v>11.42070662555821</v>
       </c>
       <c r="AB5" t="n">
-        <v>167.4970651968972</v>
+        <v>-113.7598541536329</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.40627341968369</v>
+        <v>114.3316970786444</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.98899807566241</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>13.31947762736054</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>13.31947762736054</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B-02_T-01</t>
+          <t>B-10_T-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.98007306542677</v>
+        <v>59.96993987975952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1017,101 +1017,101 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[164, 188, 202, 227, 240]</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0.4001328903654485, 0.2334108527131783, 0.41680509413067557, 0.21673864894795128]</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3167718715393134</v>
+          <t>[83, 174, 185, 264, 299]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[1.5174269005847953, 0.1834252297410192, 1.3173266499582288, 0.583625730994152]</t>
+        </is>
       </c>
       <c r="I6" t="n">
-        <v>0.0920752547695206</v>
+        <v>0.9004511278195488</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2906673951891385</v>
+        <v>0.5405896724241415</v>
       </c>
       <c r="K6" t="n">
-        <v>1.267087486157254</v>
+        <v>0.6003542621276788</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2167386489479513</v>
+        <v>3.601804511278195</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8486237691475157</v>
+        <v>0.2001002506265664</v>
       </c>
       <c r="N6" t="n">
-        <v>227</v>
+        <v>3.367033096709527</v>
       </c>
       <c r="O6" t="n">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="P6" t="n">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="Q6" t="n">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="R6" t="n">
-        <v>177.5395849793074</v>
+        <v>302</v>
       </c>
       <c r="S6" t="n">
-        <v>149.8763334973043</v>
+        <v>113.2543110788772</v>
       </c>
       <c r="T6" t="n">
-        <v>-27.66325148200312</v>
+        <v>113.5652642887525</v>
       </c>
       <c r="U6" t="n">
-        <v>165.9945061490363</v>
+        <v>0.3109532098752936</v>
       </c>
       <c r="V6" t="n">
-        <v>151.9184183153003</v>
+        <v>154.7240370916124</v>
       </c>
       <c r="W6" t="n">
-        <v>-33.34373427410514</v>
+        <v>154.7240370916124</v>
       </c>
       <c r="X6" t="n">
-        <v>-160.0439755556534</v>
+        <v>45.64906800340687</v>
       </c>
       <c r="Y6" t="n">
-        <v>163.4805148236349</v>
+        <v>-73.31191599326834</v>
       </c>
       <c r="Z6" t="n">
-        <v>-61.22102603133842</v>
+        <v>86.36245964644418</v>
       </c>
       <c r="AA6" t="n">
-        <v>-148.0669650048625</v>
+        <v>3.375911072172145</v>
       </c>
       <c r="AB6" t="n">
-        <v>160.2243432006541</v>
+        <v>-78.50106802435633</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.90390685397464</v>
+        <v>78.5736244329599</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.81346322559077</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>wrist_highest_fallback</t>
-        </is>
+        <v>34.01496588692428</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32.89982321508779</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B-05_T-01</t>
+          <t>B-04_T-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.97227783767134</v>
+        <v>59.9734630694383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1124,71 +1124,701 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>479</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0.0166743708269132</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0.005136997450433872</v>
+        <v>0.1834144542772861</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>1.300285920286601</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>181</v>
       </c>
       <c r="Q7" t="n">
-        <v>479</v>
+        <v>172</v>
       </c>
       <c r="R7" t="n">
-        <v>51.27023230070281</v>
+        <v>184</v>
       </c>
       <c r="S7" t="n">
-        <v>149.4487266203328</v>
+        <v>171.4633161734001</v>
       </c>
       <c r="T7" t="n">
-        <v>98.17849431962995</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+        <v>175.4154031157483</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.952086942348188</v>
+      </c>
+      <c r="V7" t="n">
+        <v>162.1654693207849</v>
+      </c>
       <c r="W7" t="n">
-        <v>1.424735654946313</v>
+        <v>176.362950521001</v>
       </c>
       <c r="X7" t="n">
-        <v>-91.55174835623404</v>
+        <v>-24.02364444835408</v>
       </c>
       <c r="Y7" t="n">
-        <v>91.56283361042119</v>
+        <v>-138.5119364033361</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.424735654946313</v>
+        <v>140.5798421495157</v>
       </c>
       <c r="AA7" t="n">
-        <v>-91.55174835623404</v>
+        <v>-47.30159797640707</v>
       </c>
       <c r="AB7" t="n">
-        <v>91.56283361042119</v>
+        <v>-140.5345941571037</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.868702140095831</v>
+        <v>148.2815340021254</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.868702140095831</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>speed_peak_drop</t>
-        </is>
+        <v>18.63004015970721</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>18.63004015970721</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B-09_T-08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>59.97865528281751</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0.3334519572953736</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.117390032396196</v>
+      </c>
+      <c r="O8" t="n">
+        <v>167</v>
+      </c>
+      <c r="P8" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>222</v>
+      </c>
+      <c r="R8" t="n">
+        <v>232</v>
+      </c>
+      <c r="S8" t="n">
+        <v>177.2524540269637</v>
+      </c>
+      <c r="T8" t="n">
+        <v>163.106385065699</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-14.14606896126466</v>
+      </c>
+      <c r="V8" t="n">
+        <v>152.8665716511983</v>
+      </c>
+      <c r="W8" t="n">
+        <v>156.2172648402335</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.476099322625428</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-121.294144866532</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>121.319415786422</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>48.28651399054674</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-87.22434532953777</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>99.69791297477455</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15.08436649032096</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>14.92780184371975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B-04_T-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>87</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[40, 50, 57, 67, 87]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[0.4166666666666667, 0.2916666666666667, 0.4166666666666667, 0.8333333333333334]</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4895833333333334</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2049199538844375</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4185599058065107</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.958333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.41828279889107</v>
+      </c>
+      <c r="O9" t="n">
+        <v>83</v>
+      </c>
+      <c r="P9" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>82</v>
+      </c>
+      <c r="R9" t="n">
+        <v>87</v>
+      </c>
+      <c r="S9" t="n">
+        <v>155.7744235616132</v>
+      </c>
+      <c r="T9" t="n">
+        <v>162.7551817554987</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.980758193885436</v>
+      </c>
+      <c r="V9" t="n">
+        <v>172.8897378645125</v>
+      </c>
+      <c r="W9" t="n">
+        <v>172.8897378645125</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-27.80413081551966</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-132.0470672864061</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>134.942571745714</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-72.94064013325148</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-127.8954620757157</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>147.2331015859182</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>9.292048010061194</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.292048010061194</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B-05_T-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>59.97227783767134</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>606</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[537, 556, 574, 595, 603]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[0.3168130457113508, 0.30013867488443763, 0.3501617873651772, 0.13339496661530562]</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2751271186440678</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0837876764354621</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3045416854885118</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.100508474576271</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1333949666153056</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.144597156067693</v>
+      </c>
+      <c r="O10" t="n">
+        <v>595</v>
+      </c>
+      <c r="P10" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>595</v>
+      </c>
+      <c r="R10" t="n">
+        <v>606</v>
+      </c>
+      <c r="S10" t="n">
+        <v>178.458961792157</v>
+      </c>
+      <c r="T10" t="n">
+        <v>178.4381615788259</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.020800213331114</v>
+      </c>
+      <c r="V10" t="n">
+        <v>166.3341671947343</v>
+      </c>
+      <c r="W10" t="n">
+        <v>173.2089471039032</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-25.66274561141697</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-161.2853052017411</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>163.3141946872196</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-59.20243178551527</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-160.0619194040879</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>170.6597374093823</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.51088613177059</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17.4330809864734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B-01_T-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>59.96321275291233</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>113</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[30, 48, 64, 93, 113]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[0.3001840490797546, 0.26683026584867076, 0.48362985685071574, 0.33353783231083844]</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3460455010224949</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0828616663530362</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.239453095353636</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.384182004089979</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3335378323108384</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.966445496937002</v>
+      </c>
+      <c r="O11" t="n">
+        <v>93</v>
+      </c>
+      <c r="P11" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>99</v>
+      </c>
+      <c r="R11" t="n">
+        <v>113</v>
+      </c>
+      <c r="S11" t="n">
+        <v>177.2521232537956</v>
+      </c>
+      <c r="T11" t="n">
+        <v>160.4885255879036</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-16.76359766589198</v>
+      </c>
+      <c r="V11" t="n">
+        <v>148.334486355258</v>
+      </c>
+      <c r="W11" t="n">
+        <v>148.334486355258</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.0984728272029</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-120.2839894259028</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>120.8909060143122</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-33.43981012219938</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-129.0534100547659</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>133.3154287686625</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11.65601858978028</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>11.54714147271341</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B-10_T-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>59.9791013584117</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>226</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[121, 142, 179, 186, 199]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[0.3501219512195122, 0.6168815331010453, 0.11670731707317072, 0.21674216027874565]</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3251132404181185</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1877042168725122</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5773502691896257</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.300452961672474</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2167421602787457</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.278886562935159</v>
+      </c>
+      <c r="O12" t="n">
+        <v>186</v>
+      </c>
+      <c r="P12" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>226</v>
+      </c>
+      <c r="S12" t="n">
+        <v>57.20335383272291</v>
+      </c>
+      <c r="T12" t="n">
+        <v>121.8613321221183</v>
+      </c>
+      <c r="U12" t="n">
+        <v>64.6579782893954</v>
+      </c>
+      <c r="V12" t="n">
+        <v>107.6618129929615</v>
+      </c>
+      <c r="W12" t="n">
+        <v>150.0760322867413</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22.03593212004312</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-87.36344850999672</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>90.099691675155</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>108.8322471596471</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-65.11030726095208</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>126.8219623465672</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.49382620972592</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>11.97198189849741</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B-03_T-04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>59.97088791848617</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[52, 72, 117, 138, 141]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[0.33349514563106797, 0.750364077669903, 0.35016990291262134, 0.0500242718446602]</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3710133495145631</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2493907715936242</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6721881353324056</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.484053398058252</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0500242718446602</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.047838528546654</v>
+      </c>
+      <c r="O13" t="n">
+        <v>138</v>
+      </c>
+      <c r="P13" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>130</v>
+      </c>
+      <c r="R13" t="n">
+        <v>148</v>
+      </c>
+      <c r="S13" t="n">
+        <v>177.6408059058263</v>
+      </c>
+      <c r="T13" t="n">
+        <v>158.3908943669596</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-19.24991153886671</v>
+      </c>
+      <c r="V13" t="n">
+        <v>175.3214393218934</v>
+      </c>
+      <c r="W13" t="n">
+        <v>154.9573687745823</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-26.49380917469704</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-124.9657082547615</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>127.7432979228242</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-40.31607793150386</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-126.4227325921241</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>132.6954914676411</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.93264652080351</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>13.93264652080351</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_making/master.xlsx
+++ b/dataset_making/master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,11 +588,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B-01_T-02</t>
+          <t>B-05_T-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.97322623828648</v>
+        <v>59.97227783767134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -605,101 +605,101 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>181</v>
+        <v>606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>ensemble_4signal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[86, 108, 127, 163, 174]</t>
+          <t>[537, 556, 574, 595, 603]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[0.36683035714285717, 0.31680803571428573, 0.6002678571428571, 0.18341517857142858]</t>
+          <t>[0.3168130457113508, 0.30013867488443763, 0.3501617873651772, 0.13339496661530562]</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.3668303571428572</v>
+        <v>0.2751271186440678</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1505294213582035</v>
+        <v>0.0837876764354621</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4103515928469952</v>
+        <v>0.3045416854885118</v>
       </c>
       <c r="L2" t="n">
-        <v>1.467321428571428</v>
+        <v>1.100508474576271</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1834151785714286</v>
+        <v>0.1333949666153056</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9874416733839388</v>
+        <v>1.120697362292377</v>
       </c>
       <c r="O2" t="n">
-        <v>163</v>
+        <v>595</v>
       </c>
       <c r="P2" t="n">
-        <v>174</v>
+        <v>603</v>
       </c>
       <c r="Q2" t="n">
-        <v>166</v>
+        <v>595</v>
       </c>
       <c r="R2" t="n">
-        <v>181</v>
+        <v>606</v>
       </c>
       <c r="S2" t="n">
-        <v>175.8123433432208</v>
+        <v>178.458961792157</v>
       </c>
       <c r="T2" t="n">
-        <v>165.7149479572232</v>
+        <v>178.4381615788259</v>
       </c>
       <c r="U2" t="n">
-        <v>-10.0973953859976</v>
+        <v>-0.020800213331114</v>
       </c>
       <c r="V2" t="n">
-        <v>154.2438782122022</v>
+        <v>166.3341671947343</v>
       </c>
       <c r="W2" t="n">
-        <v>134.9968098014093</v>
+        <v>173.2089471039032</v>
       </c>
       <c r="X2" t="n">
-        <v>-12.80324573103566</v>
+        <v>-25.12689391497523</v>
       </c>
       <c r="Y2" t="n">
-        <v>-134.8827113073759</v>
+        <v>-157.9175827564456</v>
       </c>
       <c r="Z2" t="n">
-        <v>135.4889992245798</v>
+        <v>159.9041079567791</v>
       </c>
       <c r="AA2" t="n">
-        <v>-51.83775993651789</v>
+        <v>-57.96625370908875</v>
       </c>
       <c r="AB2" t="n">
-        <v>-131.309876001777</v>
+        <v>-156.7197419010602</v>
       </c>
       <c r="AC2" t="n">
-        <v>141.1716575337915</v>
+        <v>167.0962718632626</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.38378390800123</v>
+        <v>17.1452495712097</v>
       </c>
       <c r="AE2" t="n">
-        <v>12.37740178354601</v>
+        <v>17.06906903848245</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B-01_T-03</t>
+          <t>B-05_T-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.98113800691606</v>
+        <v>59.97993981945837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -712,101 +712,101 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>ensemble_4signal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[97, 109, 133, 151, 174]</t>
+          <t>[188, 209, 223, 245, 252]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[0.200062893081761, 0.400125786163522, 0.30009433962264154, 0.3834538784067086]</t>
+          <t>[0.3501170568561873, 0.2334113712374582, 0.36678929765886287, 0.1167056856187291]</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.3209342243186583</v>
+        <v>0.2667558528428094</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07941062605823181</v>
+        <v>0.1007257260507842</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2474358296526967</v>
+        <v>0.3775951866748304</v>
       </c>
       <c r="L3" t="n">
-        <v>1.283736897274633</v>
+        <v>1.067023411371238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3834538784067086</v>
+        <v>0.1167056856187291</v>
       </c>
       <c r="N3" t="n">
-        <v>1.142821065595325</v>
+        <v>1.124611492589131</v>
       </c>
       <c r="O3" t="n">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="P3" t="n">
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="Q3" t="n">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="R3" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="S3" t="n">
-        <v>72.53609581180426</v>
+        <v>178.7636162094396</v>
       </c>
       <c r="T3" t="n">
-        <v>69.79052422809175</v>
+        <v>175.3729404354109</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.745571583712504</v>
+        <v>-3.390675774028693</v>
       </c>
       <c r="V3" t="n">
-        <v>150.2654004250381</v>
+        <v>173.3179881540801</v>
       </c>
       <c r="W3" t="n">
-        <v>133.3561579951623</v>
+        <v>174.2045884791386</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.53535340537529</v>
+        <v>-18.24177649983778</v>
       </c>
       <c r="Y3" t="n">
-        <v>-134.7248363863054</v>
+        <v>-158.7083792965126</v>
       </c>
       <c r="Z3" t="n">
-        <v>134.8011534439836</v>
+        <v>159.7532850015791</v>
       </c>
       <c r="AA3" t="n">
-        <v>36.2626855326865</v>
+        <v>-46.99282114933716</v>
       </c>
       <c r="AB3" t="n">
-        <v>-119.2636536836556</v>
+        <v>-160.724458216808</v>
       </c>
       <c r="AC3" t="n">
-        <v>124.6547289597048</v>
+        <v>167.4535061103829</v>
       </c>
       <c r="AD3" t="n">
-        <v>27.37344026692472</v>
+        <v>16.5424424226756</v>
       </c>
       <c r="AE3" t="n">
-        <v>26.18097555819477</v>
+        <v>16.11727009762228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B-01_T-06</t>
+          <t>B-05_T-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.972985141828</v>
+        <v>59.97088791848617</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -819,101 +819,101 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>ensemble_4signal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[39, 60, 74, 104, 111]</t>
+          <t>[73, 102, 115, 138, 145]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[0.35015765765765766, 0.23343843843843845, 0.5002252252252253, 0.11671921921921923]</t>
+          <t>[0.4835679611650486, 0.21677184466019417, 0.38351941747572815, 0.11672330097087379]</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.3001351351351352</v>
+        <v>0.3001456310679612</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1419754771723819</v>
+        <v>0.142469188665853</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4730385101646222</v>
+        <v>0.4746668747398629</v>
       </c>
       <c r="L4" t="n">
-        <v>1.20054054054054</v>
+        <v>1.200582524271845</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1167192192192192</v>
+        <v>0.1167233009708738</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9406203648276278</v>
+        <v>1.055644849163659</v>
       </c>
       <c r="O4" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="P4" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="Q4" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="R4" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="S4" t="n">
-        <v>179.3692891433796</v>
+        <v>175.7952967001215</v>
       </c>
       <c r="T4" t="n">
-        <v>168.8145672851986</v>
+        <v>172.587169549542</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.55472185818095</v>
+        <v>-3.208127150579571</v>
       </c>
       <c r="V4" t="n">
-        <v>160.2502097471716</v>
+        <v>177.0519629502604</v>
       </c>
       <c r="W4" t="n">
-        <v>147.7509820281874</v>
+        <v>176.4702612891677</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.508803805132303</v>
+        <v>-31.17705909184046</v>
       </c>
       <c r="Y4" t="n">
-        <v>-139.445660389785</v>
+        <v>-158.205885971809</v>
       </c>
       <c r="Z4" t="n">
-        <v>139.7050176040126</v>
+        <v>161.2486011404165</v>
       </c>
       <c r="AA4" t="n">
-        <v>-39.89240118567241</v>
+        <v>-53.71447629733964</v>
       </c>
       <c r="AB4" t="n">
-        <v>-134.4937829467733</v>
+        <v>-158.2903711679031</v>
       </c>
       <c r="AC4" t="n">
-        <v>140.2853567685965</v>
+        <v>167.1558750638756</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.19491007457519</v>
+        <v>16.48352101782423</v>
       </c>
       <c r="AE4" t="n">
-        <v>11.99231080687573</v>
+        <v>16.21101274688166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B-07_T-02</t>
+          <t>B-05_T-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.98083679335676</v>
+        <v>59.9644128113879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -926,89 +926,105 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[209, 229, 243, 265, 272]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[0.3335311572700297, 0.23347181008902076, 0.36688427299703263, 0.11673590504451038]</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2626557863501484</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.09750796360091819</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3712385893183016</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.050623145400593</v>
+      </c>
       <c r="M5" t="n">
-        <v>0.1167039403620873</v>
+        <v>0.1167359050445104</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3423074091036046</v>
+        <v>1.232490998530124</v>
       </c>
       <c r="O5" t="n">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="P5" t="n">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="Q5" t="n">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="R5" t="n">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="S5" t="n">
-        <v>179.2654528840065</v>
+        <v>175.7646948301545</v>
       </c>
       <c r="T5" t="n">
-        <v>166.7339224089391</v>
+        <v>178.767278691703</v>
       </c>
       <c r="U5" t="n">
-        <v>-12.53153047506734</v>
+        <v>3.002583861548459</v>
       </c>
       <c r="V5" t="n">
-        <v>72.11780083079137</v>
+        <v>171.7843914437302</v>
       </c>
       <c r="W5" t="n">
-        <v>167.7296439716362</v>
+        <v>179.7229832789735</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.001252233836396</v>
+        <v>-32.93882818459798</v>
       </c>
       <c r="Y5" t="n">
-        <v>-101.7769831467103</v>
+        <v>-160.6227992385867</v>
       </c>
       <c r="Z5" t="n">
-        <v>101.7819080410734</v>
+        <v>163.9653928041334</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.42070662555821</v>
+        <v>-58.57921674568004</v>
       </c>
       <c r="AB5" t="n">
-        <v>-113.7598541536329</v>
+        <v>-158.9283080161529</v>
       </c>
       <c r="AC5" t="n">
-        <v>114.3316970786444</v>
+        <v>169.3804348896723</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.31947762736054</v>
+        <v>16.93755524660863</v>
       </c>
       <c r="AE5" t="n">
-        <v>13.31947762736054</v>
+        <v>16.72026387788978</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B-10_T-02</t>
+          <t>B-05_T-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.96993987975952</v>
+        <v>59.9790283117791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1017,101 +1033,101 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>ensemble_4signal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[83, 174, 185, 264, 299]</t>
+          <t>[182, 202, 215, 237, 244]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[1.5174269005847953, 0.1834252297410192, 1.3173266499582288, 0.583625730994152]</t>
+          <t>[0.33344988344988347, 0.21674242424242424, 0.3667948717948718, 0.11670745920745922]</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9004511278195488</v>
+        <v>0.2584236596736597</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5405896724241415</v>
+        <v>0.0989874496241709</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6003542621276788</v>
+        <v>0.3830432931302554</v>
       </c>
       <c r="L6" t="n">
-        <v>3.601804511278195</v>
+        <v>1.033694638694639</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2001002506265664</v>
+        <v>0.1167074592074592</v>
       </c>
       <c r="N6" t="n">
-        <v>3.367033096709527</v>
+        <v>1.050334154970859</v>
       </c>
       <c r="O6" t="n">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="P6" t="n">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="Q6" t="n">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="R6" t="n">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="S6" t="n">
-        <v>113.2543110788772</v>
+        <v>177.931451647667</v>
       </c>
       <c r="T6" t="n">
-        <v>113.5652642887525</v>
+        <v>177.433561693749</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3109532098752936</v>
+        <v>-0.497889953918019</v>
       </c>
       <c r="V6" t="n">
-        <v>154.7240370916124</v>
+        <v>177.4260868031231</v>
       </c>
       <c r="W6" t="n">
-        <v>154.7240370916124</v>
+        <v>179.1123140666054</v>
       </c>
       <c r="X6" t="n">
-        <v>45.64906800340687</v>
+        <v>-23.68405123340836</v>
       </c>
       <c r="Y6" t="n">
-        <v>-73.31191599326834</v>
+        <v>-158.7950322842111</v>
       </c>
       <c r="Z6" t="n">
-        <v>86.36245964644418</v>
+        <v>160.5515386440453</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.375911072172145</v>
+        <v>-53.24841492322028</v>
       </c>
       <c r="AB6" t="n">
-        <v>-78.50106802435633</v>
+        <v>-166.4013173920767</v>
       </c>
       <c r="AC6" t="n">
-        <v>78.5736244329599</v>
+        <v>174.7134571853413</v>
       </c>
       <c r="AD6" t="n">
-        <v>34.01496588692428</v>
+        <v>16.13092501035118</v>
       </c>
       <c r="AE6" t="n">
-        <v>32.89982321508779</v>
+        <v>15.8824468813813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B-04_T-09</t>
+          <t>B-05_T-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.9734630694383</v>
+        <v>59.97191011235955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1124,85 +1140,101 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>351</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>ensemble_4signal</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[285, 305, 319, 336, 348]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[0.3334894613583138, 0.23344262295081966, 0.2834660421545667, 0.2000936768149883]</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2626229508196721</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0505418104503705</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1924500897298753</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.050491803278688</v>
+      </c>
       <c r="M7" t="n">
-        <v>0.1834144542772861</v>
+        <v>0.2000936768149883</v>
       </c>
       <c r="N7" t="n">
-        <v>1.300285920286601</v>
+        <v>1.104604668052104</v>
       </c>
       <c r="O7" t="n">
-        <v>170</v>
+        <v>336</v>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>348</v>
       </c>
       <c r="Q7" t="n">
-        <v>172</v>
+        <v>340</v>
       </c>
       <c r="R7" t="n">
-        <v>184</v>
+        <v>351</v>
       </c>
       <c r="S7" t="n">
-        <v>171.4633161734001</v>
+        <v>171.041323780735</v>
       </c>
       <c r="T7" t="n">
-        <v>175.4154031157483</v>
+        <v>170.1228775184067</v>
       </c>
       <c r="U7" t="n">
-        <v>3.952086942348188</v>
+        <v>-0.9184462623283024</v>
       </c>
       <c r="V7" t="n">
-        <v>162.1654693207849</v>
+        <v>178.6087357226792</v>
       </c>
       <c r="W7" t="n">
-        <v>176.362950521001</v>
+        <v>171.4646536765978</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.02364444835408</v>
+        <v>-21.13216307830808</v>
       </c>
       <c r="Y7" t="n">
-        <v>-138.5119364033361</v>
+        <v>-153.4747483263016</v>
       </c>
       <c r="Z7" t="n">
-        <v>140.5798421495157</v>
+        <v>154.9227765378281</v>
       </c>
       <c r="AA7" t="n">
-        <v>-47.30159797640707</v>
+        <v>-29.76164947128295</v>
       </c>
       <c r="AB7" t="n">
-        <v>-140.5345941571037</v>
+        <v>-148.0556326303482</v>
       </c>
       <c r="AC7" t="n">
-        <v>148.2815340021254</v>
+        <v>151.0173040840822</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.63004015970721</v>
+        <v>15.945391962667</v>
       </c>
       <c r="AE7" t="n">
-        <v>18.63004015970721</v>
+        <v>15.65176445871277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B-09_T-08</t>
+          <t>B-05_T-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.97865528281751</v>
+        <v>59.9677592692101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1215,85 +1247,101 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232</v>
+        <v>306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>ensemble_4signal</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[236, 260, 274, 294, 305]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[0.4002150537634409, 0.23345878136200718, 0.3335125448028674, 0.18343189964157708]</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2876545698924731</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0845168102817639</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2938135497494681</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.150618279569893</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.3334519572953736</v>
+        <v>0.1834318996415771</v>
       </c>
       <c r="N8" t="n">
-        <v>1.117390032396196</v>
+        <v>1.131695531298817</v>
       </c>
       <c r="O8" t="n">
-        <v>167</v>
+        <v>294</v>
       </c>
       <c r="P8" t="n">
-        <v>187</v>
+        <v>305</v>
       </c>
       <c r="Q8" t="n">
-        <v>222</v>
+        <v>295</v>
       </c>
       <c r="R8" t="n">
-        <v>232</v>
+        <v>306</v>
       </c>
       <c r="S8" t="n">
-        <v>177.2524540269637</v>
+        <v>178.961544127159</v>
       </c>
       <c r="T8" t="n">
-        <v>163.106385065699</v>
+        <v>167.8956170129403</v>
       </c>
       <c r="U8" t="n">
-        <v>-14.14606896126466</v>
+        <v>-11.06592711421865</v>
       </c>
       <c r="V8" t="n">
-        <v>152.8665716511983</v>
+        <v>179.2412626620072</v>
       </c>
       <c r="W8" t="n">
-        <v>156.2172648402335</v>
+        <v>176.4477394170794</v>
       </c>
       <c r="X8" t="n">
-        <v>2.476099322625428</v>
+        <v>-3.015969120431731</v>
       </c>
       <c r="Y8" t="n">
-        <v>-121.294144866532</v>
+        <v>-151.2928429366229</v>
       </c>
       <c r="Z8" t="n">
-        <v>121.319415786422</v>
+        <v>151.3229010876445</v>
       </c>
       <c r="AA8" t="n">
-        <v>48.28651399054674</v>
+        <v>-56.97840892065302</v>
       </c>
       <c r="AB8" t="n">
-        <v>-87.22434532953777</v>
+        <v>-159.6355446151412</v>
       </c>
       <c r="AC8" t="n">
-        <v>99.69791297477455</v>
+        <v>169.4993987827152</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.08436649032096</v>
+        <v>15.62562912946462</v>
       </c>
       <c r="AE8" t="n">
-        <v>14.92780184371975</v>
+        <v>15.19833955008677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B-04_T-01</t>
+          <t>B-05_T-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>59.97888067581837</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1306,7 +1354,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1315,92 +1363,92 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[40, 50, 57, 67, 87]</t>
+          <t>[159, 184, 195, 217, 231]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[0.4166666666666667, 0.2916666666666667, 0.4166666666666667, 0.8333333333333334]</t>
+          <t>[0.4168133802816901, 0.18339788732394366, 0.3667957746478873, 0.23341549295774647]</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.3001056338028169</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2049199538844375</v>
+        <v>0.0950480746099369</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4185599058065107</v>
+        <v>0.3167153958608717</v>
       </c>
       <c r="L9" t="n">
-        <v>1.958333333333333</v>
+        <v>1.200422535211267</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2334154929577465</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41828279889107</v>
+        <v>1.165068961587171</v>
       </c>
       <c r="O9" t="n">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="P9" t="n">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="Q9" t="n">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="R9" t="n">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="S9" t="n">
-        <v>155.7744235616132</v>
+        <v>173.0868266116627</v>
       </c>
       <c r="T9" t="n">
-        <v>162.7551817554987</v>
+        <v>176.4306313118799</v>
       </c>
       <c r="U9" t="n">
-        <v>6.980758193885436</v>
+        <v>3.343804700217248</v>
       </c>
       <c r="V9" t="n">
-        <v>172.8897378645125</v>
+        <v>178.8724948544011</v>
       </c>
       <c r="W9" t="n">
-        <v>172.8897378645125</v>
+        <v>178.8724948544011</v>
       </c>
       <c r="X9" t="n">
-        <v>-27.80413081551966</v>
+        <v>8.700442152039439</v>
       </c>
       <c r="Y9" t="n">
-        <v>-132.0470672864061</v>
+        <v>-154.688167102129</v>
       </c>
       <c r="Z9" t="n">
-        <v>134.942571745714</v>
+        <v>154.9326522559308</v>
       </c>
       <c r="AA9" t="n">
-        <v>-72.94064013325148</v>
+        <v>-40.55341975975243</v>
       </c>
       <c r="AB9" t="n">
-        <v>-127.8954620757157</v>
+        <v>-153.2135437014947</v>
       </c>
       <c r="AC9" t="n">
-        <v>147.2331015859182</v>
+        <v>158.4896521157785</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.292048010061194</v>
+        <v>16.62920379858529</v>
       </c>
       <c r="AE9" t="n">
-        <v>9.292048010061194</v>
+        <v>16.46361706406108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B-05_T-01</t>
+          <t>B-05_T-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.97227783767134</v>
+        <v>59.9670510708402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1413,7 +1461,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>606</v>
+        <v>276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1422,92 +1470,92 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[537, 556, 574, 595, 603]</t>
+          <t>[203, 229, 246, 268, 273]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[0.3168130457113508, 0.30013867488443763, 0.3501617873651772, 0.13339496661530562]</t>
+          <t>[0.43357142857142855, 0.28348901098901097, 0.3668681318681319, 0.08337912087912087]</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2751271186440678</v>
+        <v>0.291826923076923</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0837876764354621</v>
+        <v>0.1315700335123917</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3045416854885118</v>
+        <v>0.4508495382302715</v>
       </c>
       <c r="L10" t="n">
-        <v>1.100508474576271</v>
+        <v>1.167307692307693</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1333949666153056</v>
+        <v>0.0833791208791208</v>
       </c>
       <c r="N10" t="n">
-        <v>1.144597156067693</v>
+        <v>1.160812218552888</v>
       </c>
       <c r="O10" t="n">
-        <v>595</v>
+        <v>268</v>
       </c>
       <c r="P10" t="n">
-        <v>603</v>
+        <v>273</v>
       </c>
       <c r="Q10" t="n">
-        <v>595</v>
+        <v>265</v>
       </c>
       <c r="R10" t="n">
-        <v>606</v>
+        <v>276</v>
       </c>
       <c r="S10" t="n">
-        <v>178.458961792157</v>
+        <v>178.7192942327834</v>
       </c>
       <c r="T10" t="n">
-        <v>178.4381615788259</v>
+        <v>168.0322978608039</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.020800213331114</v>
+        <v>-10.68699637197946</v>
       </c>
       <c r="V10" t="n">
-        <v>166.3341671947343</v>
+        <v>176.0523795586224</v>
       </c>
       <c r="W10" t="n">
-        <v>173.2089471039032</v>
+        <v>174.4718666163072</v>
       </c>
       <c r="X10" t="n">
-        <v>-25.66274561141697</v>
+        <v>-15.32152989378921</v>
       </c>
       <c r="Y10" t="n">
-        <v>-161.2853052017411</v>
+        <v>-154.2573406550321</v>
       </c>
       <c r="Z10" t="n">
-        <v>163.3141946872196</v>
+        <v>155.0163746971554</v>
       </c>
       <c r="AA10" t="n">
-        <v>-59.20243178551527</v>
+        <v>-35.80446939690157</v>
       </c>
       <c r="AB10" t="n">
-        <v>-160.0619194040879</v>
+        <v>-159.7320527514247</v>
       </c>
       <c r="AC10" t="n">
-        <v>170.6597374093823</v>
+        <v>163.6957198737266</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.51088613177059</v>
+        <v>16.9515123269308</v>
       </c>
       <c r="AE10" t="n">
-        <v>17.4330809864734</v>
+        <v>16.47441865598067</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B-01_T-01</t>
+          <t>B-05_T-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.96321275291233</v>
+        <v>59.97403721332756</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1520,7 +1568,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1529,96 +1577,96 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[30, 48, 64, 93, 113]</t>
+          <t>[111, 136, 150, 173, 180]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[0.3001840490797546, 0.26683026584867076, 0.48362985685071574, 0.33353783231083844]</t>
+          <t>[0.41684704184704185, 0.23343434343434344, 0.3834992784992785, 0.11671717171717172]</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3460455010224949</v>
+        <v>0.2876244588744589</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0828616663530362</v>
+        <v>0.1204536491799587</v>
       </c>
       <c r="K11" t="n">
-        <v>0.239453095353636</v>
+        <v>0.4187879210666634</v>
       </c>
       <c r="L11" t="n">
-        <v>1.384182004089979</v>
+        <v>1.150497835497835</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3335378323108384</v>
+        <v>0.1167171717171717</v>
       </c>
       <c r="N11" t="n">
-        <v>0.966445496937002</v>
+        <v>1.127863282202866</v>
       </c>
       <c r="O11" t="n">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="P11" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="Q11" t="n">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="R11" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="S11" t="n">
-        <v>177.2521232537956</v>
+        <v>172.7424337572813</v>
       </c>
       <c r="T11" t="n">
-        <v>160.4885255879036</v>
+        <v>169.2593351252305</v>
       </c>
       <c r="U11" t="n">
-        <v>-16.76359766589198</v>
+        <v>-3.483098632050769</v>
       </c>
       <c r="V11" t="n">
-        <v>148.334486355258</v>
+        <v>179.076376492534</v>
       </c>
       <c r="W11" t="n">
-        <v>148.334486355258</v>
+        <v>176.9867854932333</v>
       </c>
       <c r="X11" t="n">
-        <v>12.0984728272029</v>
+        <v>-10.10120122530614</v>
       </c>
       <c r="Y11" t="n">
-        <v>-120.2839894259028</v>
+        <v>-159.5679762416461</v>
       </c>
       <c r="Z11" t="n">
-        <v>120.8909060143122</v>
+        <v>159.8873769503041</v>
       </c>
       <c r="AA11" t="n">
-        <v>-33.43981012219938</v>
+        <v>-42.00730540528799</v>
       </c>
       <c r="AB11" t="n">
-        <v>-129.0534100547659</v>
+        <v>-160.3237657976316</v>
       </c>
       <c r="AC11" t="n">
-        <v>133.3154287686625</v>
+        <v>165.7357040198248</v>
       </c>
       <c r="AD11" t="n">
-        <v>11.65601858978028</v>
+        <v>17.22323299325653</v>
       </c>
       <c r="AE11" t="n">
-        <v>11.54714147271341</v>
+        <v>16.81034562218418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B-10_T-04</t>
+          <t>B-06_T-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.9791013584117</v>
+        <v>59.97116770783277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1627,7 +1675,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1636,189 +1684,2008 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[121, 142, 179, 186, 199]</t>
+          <t>[53, 36, 56, 76, 106]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[0.3501219512195122, 0.6168815331010453, 0.11670731707317072, 0.21674216027874565]</t>
+          <t>[-0.2834695512820513, 0.3334935897435898, 0.3334935897435898, 0.5002403846153847]</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3251132404181185</v>
+        <v>0.2209395032051282</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1877042168725122</v>
+        <v>0.2990711961215137</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5773502691896257</v>
+        <v>1.353633876164939</v>
       </c>
       <c r="L12" t="n">
-        <v>1.300452961672474</v>
+        <v>0.8837580128205129</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2167421602787457</v>
+        <v>0.5002403846153847</v>
       </c>
       <c r="N12" t="n">
-        <v>0.278886562935159</v>
+        <v>1.20512080637569</v>
       </c>
       <c r="O12" t="n">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="P12" t="n">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="n">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="R12" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="S12" t="n">
-        <v>57.20335383272291</v>
+        <v>153.4002496899343</v>
       </c>
       <c r="T12" t="n">
-        <v>121.8613321221183</v>
+        <v>140.4637736667917</v>
       </c>
       <c r="U12" t="n">
-        <v>64.6579782893954</v>
+        <v>-12.93647602314257</v>
       </c>
       <c r="V12" t="n">
-        <v>107.6618129929615</v>
+        <v>143.3822942760024</v>
       </c>
       <c r="W12" t="n">
-        <v>150.0760322867413</v>
+        <v>176.39128718827</v>
       </c>
       <c r="X12" t="n">
-        <v>22.03593212004312</v>
+        <v>18.7298407459259</v>
       </c>
       <c r="Y12" t="n">
-        <v>-87.36344850999672</v>
+        <v>-145.353934882164</v>
       </c>
       <c r="Z12" t="n">
-        <v>90.099691675155</v>
+        <v>146.5557004012335</v>
       </c>
       <c r="AA12" t="n">
-        <v>108.8322471596471</v>
+        <v>51.65007253932951</v>
       </c>
       <c r="AB12" t="n">
-        <v>-65.11030726095208</v>
+        <v>-103.5951266498566</v>
       </c>
       <c r="AC12" t="n">
-        <v>126.8219623465672</v>
+        <v>115.7569879485373</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.49382620972592</v>
+        <v>10.41753388262761</v>
       </c>
       <c r="AE12" t="n">
-        <v>11.97198189849741</v>
+        <v>10.13996425336765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B-03_T-04</t>
+          <t>B-06_T-02</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>59.97521685254027</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>206</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[115, 136, 157, 190, 200]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[0.35014462809917357, 0.35014462809917357, 0.5502272727272728, 0.16673553719008266]</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3543130165289257</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1356488642240216</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3828503551828936</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.417252066115702</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1667355371900827</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8672196512357518</v>
+      </c>
+      <c r="O13" t="n">
+        <v>190</v>
+      </c>
+      <c r="P13" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>191</v>
+      </c>
+      <c r="R13" t="n">
+        <v>206</v>
+      </c>
+      <c r="S13" t="n">
+        <v>159.2963917302428</v>
+      </c>
+      <c r="T13" t="n">
+        <v>151.4447228077553</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-7.851668922487505</v>
+      </c>
+      <c r="V13" t="n">
+        <v>170.468775381035</v>
+      </c>
+      <c r="W13" t="n">
+        <v>157.8806183764622</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-13.38490611599976</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-126.3720712926623</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>127.0789365494213</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.415955842139573</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-114.0442543042216</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>114.1297183287758</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.12681946285489</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>10.77049224888695</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B-06_T-03</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>59.97088791848617</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" t="n">
+        <v>161</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[56, 83, 116, 154, 155]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[0.45021844660194177, 0.5502669902912621, 0.6336407766990292, 0.016674757281553397]</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4127002427184466</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2376884149109702</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5759347591979165</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.650800970873787</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0166747572815534</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9707819354024348</v>
+      </c>
+      <c r="O14" t="n">
+        <v>154</v>
+      </c>
+      <c r="P14" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>146</v>
+      </c>
+      <c r="R14" t="n">
+        <v>161</v>
+      </c>
+      <c r="S14" t="n">
+        <v>162.623732225177</v>
+      </c>
+      <c r="T14" t="n">
+        <v>153.1304345735178</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-9.493297651659162</v>
+      </c>
+      <c r="V14" t="n">
+        <v>170.6727232238318</v>
+      </c>
+      <c r="W14" t="n">
+        <v>170.6943454058215</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-43.63842826894862</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-115.7852524339536</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>123.735755151769</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-45.27820037413044</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-117.4562154768485</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>125.8812058381384</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11.38969998607052</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>11.11068643971326</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B-06_T-04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>59.97458703939009</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[99, 125, 154, 186, 188]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[0.4335169491525424, 0.48353813559322034, 0.5335593220338983, 0.033347457627118646]</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3709904661016949</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1981211580583645</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5340330174524109</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.48396186440678</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0333474576271186</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5978287991149214</v>
+      </c>
+      <c r="O15" t="n">
+        <v>186</v>
+      </c>
+      <c r="P15" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>191</v>
+      </c>
+      <c r="R15" t="n">
+        <v>205</v>
+      </c>
+      <c r="S15" t="n">
+        <v>142.1977934792533</v>
+      </c>
+      <c r="T15" t="n">
+        <v>131.3439390249841</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-10.85385445426917</v>
+      </c>
+      <c r="V15" t="n">
+        <v>157.7606620633938</v>
+      </c>
+      <c r="W15" t="n">
+        <v>172.8031610365505</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-41.96922108828562</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-115.4820136342942</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>122.871929226283</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-30.02256129420896</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-111.904367688497</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>115.8617352469178</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11.58414571558969</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>11.06316753144177</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B-06_T-05</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>59.9750104123282</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>191</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[83, 116, 138, 171, 185]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[0.5502291666666667, 0.3668194444444445, 0.5502291666666667, 0.23343055555555556]</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4251770833333334</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1336491601390876</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.3143376380761057</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.700708333333333</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2334305555555556</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.098716658833067</v>
+      </c>
+      <c r="O16" t="n">
+        <v>171</v>
+      </c>
+      <c r="P16" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>177</v>
+      </c>
+      <c r="R16" t="n">
+        <v>191</v>
+      </c>
+      <c r="S16" t="n">
+        <v>136.4190768675963</v>
+      </c>
+      <c r="T16" t="n">
+        <v>116.6477255579098</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-19.77135130968651</v>
+      </c>
+      <c r="V16" t="n">
+        <v>172.8342047253501</v>
+      </c>
+      <c r="W16" t="n">
+        <v>172.4924406822612</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-25.84039752177584</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-125.2180419624629</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>127.8564983760956</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-27.64964237650357</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-118.6689141591258</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>121.8475026878044</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11.52642091281803</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>11.06711596760857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B-07_T-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>59.97403721332756</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>164</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[64, 87, 113, 152, 162]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[0.3834992784992785, 0.43352092352092353, 0.6502813852813852, 0.16673881673881674]</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.408510101010101</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1718704383261618</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4207250638385368</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.634040404040404</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1667388167388167</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8804397140445316</v>
+      </c>
+      <c r="O17" t="n">
+        <v>152</v>
+      </c>
+      <c r="P17" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q17" t="n">
         <v>148</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="R17" t="n">
+        <v>164</v>
+      </c>
+      <c r="S17" t="n">
+        <v>177.731696739278</v>
+      </c>
+      <c r="T17" t="n">
+        <v>166.757020078879</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-10.97467666039898</v>
+      </c>
+      <c r="V17" t="n">
+        <v>165.0748044428065</v>
+      </c>
+      <c r="W17" t="n">
+        <v>169.3612002839166</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-17.44276086342975</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-134.7425784878479</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>135.8668920822606</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-44.76198242628927</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-135.2969153125029</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>142.5092641332837</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.56772634518207</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>12.56772634518207</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B-07_T-02</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>59.98083679335676</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>231</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>ensemble_4signal</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[52, 72, 117, 138, 141]</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[0.33349514563106797, 0.750364077669903, 0.35016990291262134, 0.0500242718446602]</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.3710133495145631</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.2493907715936242</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.6721881353324056</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.484053398058252</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0500242718446602</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.047838528546654</v>
-      </c>
-      <c r="O13" t="n">
-        <v>138</v>
-      </c>
-      <c r="P13" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>130</v>
-      </c>
-      <c r="R13" t="n">
-        <v>148</v>
-      </c>
-      <c r="S13" t="n">
-        <v>177.6408059058263</v>
-      </c>
-      <c r="T13" t="n">
-        <v>158.3908943669596</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-19.24991153886671</v>
-      </c>
-      <c r="V13" t="n">
-        <v>175.3214393218934</v>
-      </c>
-      <c r="W13" t="n">
-        <v>154.9573687745823</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-26.49380917469704</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-124.9657082547615</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>127.7432979228242</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-40.31607793150386</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-126.4227325921241</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>132.6954914676411</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.93264652080351</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>13.93264652080351</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[140, 163, 184, 200, 207]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[0.38345580404685836, 0.350111821086262, 0.266751863684771, 0.11670394036208732]</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2792558572949946</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1030262976897743</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3689315550539785</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.117023429179979</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1167039403620873</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3316114818705365</v>
+      </c>
+      <c r="O18" t="n">
+        <v>200</v>
+      </c>
+      <c r="P18" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>215</v>
+      </c>
+      <c r="R18" t="n">
+        <v>231</v>
+      </c>
+      <c r="S18" t="n">
+        <v>179.2654528840065</v>
+      </c>
+      <c r="T18" t="n">
+        <v>171.8369840523552</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-7.428468831651287</v>
+      </c>
+      <c r="V18" t="n">
+        <v>72.11780083079137</v>
+      </c>
+      <c r="W18" t="n">
+        <v>171.9146543192668</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.96996655099621</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-98.596803060661</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>98.60157406904224</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>11.06384888959195</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-110.205250631442</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>110.7592254351333</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.90328983914469</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>12.61524631601207</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B-08_T-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>59.97422311327509</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>387</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[310, 332, 350, 376, 382]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[0.3668242597898759, 0.30012893982808025, 0.43351957975167144, 0.10004297994269341]</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3001289398280802</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.124775518299152</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4157397096415491</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.200515759312322</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1000429799426934</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6433076061121383</v>
+      </c>
+      <c r="O19" t="n">
+        <v>376</v>
+      </c>
+      <c r="P19" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>377</v>
+      </c>
+      <c r="R19" t="n">
+        <v>387</v>
+      </c>
+      <c r="S19" t="n">
+        <v>178.1956980646104</v>
+      </c>
+      <c r="T19" t="n">
+        <v>149.895197460704</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-28.30050060390633</v>
+      </c>
+      <c r="V19" t="n">
+        <v>166.6463597039572</v>
+      </c>
+      <c r="W19" t="n">
+        <v>166.2180688657243</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-12.61383731784999</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-116.5650977317725</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>117.2456007750349</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-48.71329014908127</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-111.6309206689977</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>121.7967449752112</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10.85367958502181</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>10.26821664843971</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B-08_T-02</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>59.97474747474747</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>262</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[193, 207, 225, 253, 257]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[0.23343157894736843, 0.3001263157894737, 0.46686315789473687, 0.06669473684210526]</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2667789473684211</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1434324549789002</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5376453291901642</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.067115789473684</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0666947368421052</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.5761167556076191</v>
+      </c>
+      <c r="O20" t="n">
+        <v>253</v>
+      </c>
+      <c r="P20" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>253</v>
+      </c>
+      <c r="R20" t="n">
+        <v>262</v>
+      </c>
+      <c r="S20" t="n">
+        <v>177.8490736821456</v>
+      </c>
+      <c r="T20" t="n">
+        <v>145.1593624331974</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-32.68971124894821</v>
+      </c>
+      <c r="V20" t="n">
+        <v>167.8150556920381</v>
+      </c>
+      <c r="W20" t="n">
+        <v>169.6534449467283</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-4.262754323222834</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-112.1851989113458</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>112.2661566510512</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-37.14333394494386</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-108.4972616148467</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>114.6790435714656</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.35115133428089</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>10.57875353555545</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B-08_T-03</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>59.97171145685997</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>251</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[178, 195, 213, 241, 245]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[0.28346698113207547, 0.3001415094339623, 0.4668867924528302, 0.06669811320754718]</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2792983490566038</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1421619667903398</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5089968031337294</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.117193396226415</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.06669811320754709</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.6107182582254673</v>
+      </c>
+      <c r="O21" t="n">
+        <v>241</v>
+      </c>
+      <c r="P21" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>242</v>
+      </c>
+      <c r="R21" t="n">
+        <v>251</v>
+      </c>
+      <c r="S21" t="n">
+        <v>171.9800915729763</v>
+      </c>
+      <c r="T21" t="n">
+        <v>153.314733972659</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-18.66535760031724</v>
+      </c>
+      <c r="V21" t="n">
+        <v>163.178268255645</v>
+      </c>
+      <c r="W21" t="n">
+        <v>167.2440453913964</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-18.23427580705023</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-110.5852986280045</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>112.078530891748</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-45.12083066084291</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-104.1050322458035</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>113.4625361007952</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10.39473460600514</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.851790636811231</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B-08_T-04</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>59.97966790918333</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>154</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[77, 97, 112, 143, 150]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[0.3334463276836158, 0.2500847457627119, 0.5168418079096045, 0.11670621468926554]</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3042697740112995</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1450467570748361</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.4767044559261731</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.217079096045198</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1167062146892655</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5854256475969936</v>
+      </c>
+      <c r="O22" t="n">
+        <v>143</v>
+      </c>
+      <c r="P22" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>145</v>
+      </c>
+      <c r="R22" t="n">
+        <v>154</v>
+      </c>
+      <c r="S22" t="n">
+        <v>177.3928902525483</v>
+      </c>
+      <c r="T22" t="n">
+        <v>150.459681240913</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-26.93320901163537</v>
+      </c>
+      <c r="V22" t="n">
+        <v>168.8372818550783</v>
+      </c>
+      <c r="W22" t="n">
+        <v>166.1775428123005</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-8.062954149814654</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-111.9577433559868</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>112.247706110134</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-51.19983014508696</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-106.2896615363139</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>117.9784503898484</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10.52382084950422</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>10.04090297061736</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B-08_T-05</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>59.96621621621622</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[148, 165, 182, 208, 214]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[0.28349295774647887, 0.28349295774647887, 0.4335774647887324, 0.10005633802816902]</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2751549295774648</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1182119514397836</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4296196023866007</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.100619718309859</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.100056338028169</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.6359978033769687</v>
+      </c>
+      <c r="O23" t="n">
+        <v>208</v>
+      </c>
+      <c r="P23" t="n">
+        <v>214</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>211</v>
+      </c>
+      <c r="R23" t="n">
+        <v>220</v>
+      </c>
+      <c r="S23" t="n">
+        <v>175.7955657474623</v>
+      </c>
+      <c r="T23" t="n">
+        <v>146.5222239216202</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-29.27334182584218</v>
+      </c>
+      <c r="V23" t="n">
+        <v>171.5444928115582</v>
+      </c>
+      <c r="W23" t="n">
+        <v>171.898204286035</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-16.27874397351906</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-114.1204166504943</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>115.2756132138875</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-48.01771444302162</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-107.2777126821499</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>117.5338612428158</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.89470434362034</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>10.29541909710627</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B-08_T-06</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>59.96924654023578</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>315</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[249, 269, 282, 303, 309]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[0.3335042735042735, 0.21677777777777776, 0.35017948717948716, 0.10005128205128204]</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2501282051282051</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1007436867285599</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.4027681991198191</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.000512820512821</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.100051282051282</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.6491645912913344</v>
+      </c>
+      <c r="O24" t="n">
+        <v>303</v>
+      </c>
+      <c r="P24" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>305</v>
+      </c>
+      <c r="R24" t="n">
+        <v>315</v>
+      </c>
+      <c r="S24" t="n">
+        <v>174.699472415686</v>
+      </c>
+      <c r="T24" t="n">
+        <v>152.2293335668438</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-22.47013884884217</v>
+      </c>
+      <c r="V24" t="n">
+        <v>173.1962171739914</v>
+      </c>
+      <c r="W24" t="n">
+        <v>174.5570775170949</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-19.41558503153333</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-112.8102879845245</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>114.4688866778569</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-46.59028309505765</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-103.6418457899955</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>113.6322431250692</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11.71705322755114</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>10.52412160139538</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B-08_T-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>59.96553704767375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[109, 120, 192, 205, 218]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[0.18343869731800766, 1.2006896551724138, 0.2167911877394636, 0.2167911877394636]</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4544276819923372</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4310696490217785</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9485990094878231</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.817710727969349</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2167911877394636</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.688324917169012</v>
+      </c>
+      <c r="O25" t="n">
+        <v>205</v>
+      </c>
+      <c r="P25" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>211</v>
+      </c>
+      <c r="R25" t="n">
+        <v>221</v>
+      </c>
+      <c r="S25" t="n">
+        <v>166.1747786119963</v>
+      </c>
+      <c r="T25" t="n">
+        <v>69.45726645986711</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-96.71751215212925</v>
+      </c>
+      <c r="V25" t="n">
+        <v>146.1333922367279</v>
+      </c>
+      <c r="W25" t="n">
+        <v>176.6531958301434</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-3.152706734037856</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-140.2757304073167</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>140.3111545852896</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-5.674044682671868</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-130.0953611907196</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>130.2190377264582</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>63.58167086325849</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>63.58167086325849</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B-11_T-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>59.97074597757192</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>146</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[72, 83, 100, 124, 139]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[0.18342276422764228, 0.28347154471544717, 0.40019512195121953, 0.2501219512195122]</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2793028455284553</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0785443109564752</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2812155773345787</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.117211382113821</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2501219512195122</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.9202383333228156</v>
+      </c>
+      <c r="O26" t="n">
+        <v>124</v>
+      </c>
+      <c r="P26" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>134</v>
+      </c>
+      <c r="R26" t="n">
+        <v>146</v>
+      </c>
+      <c r="S26" t="n">
+        <v>176.6586403096761</v>
+      </c>
+      <c r="T26" t="n">
+        <v>160.2398599626283</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-16.41878034704777</v>
+      </c>
+      <c r="V26" t="n">
+        <v>146.3277321620363</v>
+      </c>
+      <c r="W26" t="n">
+        <v>132.6899741787769</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-11.70981295548366</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-114.9775303007134</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>115.5722812507561</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-34.49069573489378</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-105.7733654634631</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>111.2547209503684</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12.89790984876423</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>12.63500054837541</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B-11_T-04</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>59.96332518337408</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>253</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[178, 190, 205, 232, 246]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[0.20012232415902143, 0.25015290519877675, 0.4502752293577982, 0.23347604485219164]</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.283506625891947</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0979543753498171</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.3455100036609038</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.134026503567788</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2334760448521916</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.040852328710609</v>
+      </c>
+      <c r="O27" t="n">
+        <v>232</v>
+      </c>
+      <c r="P27" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>242</v>
+      </c>
+      <c r="R27" t="n">
+        <v>253</v>
+      </c>
+      <c r="S27" t="n">
+        <v>178.2943732586486</v>
+      </c>
+      <c r="T27" t="n">
+        <v>160.3410018106511</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-17.9533714479976</v>
+      </c>
+      <c r="V27" t="n">
+        <v>143.4346910485012</v>
+      </c>
+      <c r="W27" t="n">
+        <v>129.9414501176602</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-25.06925017169242</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-109.4499654338486</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>112.2842920342892</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-34.59938567472611</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-101.9523135710888</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>107.6633258429538</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.49677827967506</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>13.3406887717418</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B-11_T-05</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>59.9677592692101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>291</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[207, 226, 267, 269, 284]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[0.31683691756272403, 0.6837007168458782, 0.03335125448028674, 0.2501344086021505]</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3210058243727598</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.2341649386455154</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.7294725542848634</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.284023297491039</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2501344086021505</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.034958107931903</v>
+      </c>
+      <c r="O28" t="n">
+        <v>269</v>
+      </c>
+      <c r="P28" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>279</v>
+      </c>
+      <c r="R28" t="n">
+        <v>291</v>
+      </c>
+      <c r="S28" t="n">
+        <v>178.1073991850874</v>
+      </c>
+      <c r="T28" t="n">
+        <v>172.7067235435442</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-5.400675641543188</v>
+      </c>
+      <c r="V28" t="n">
+        <v>147.086491414609</v>
+      </c>
+      <c r="W28" t="n">
+        <v>135.2529660052642</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-23.49511829723009</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-112.3679957563227</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>114.7980272221339</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-43.46474751559172</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-103.3069836876609</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>112.0781743036385</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>13.98945433485522</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>13.72210762842999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B-11_T-06</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>59.97340425531915</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>407</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[312, 336, 351, 388, 394]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[0.40017738359201777, 0.2501108647450111, 0.616940133037694, 0.10004434589800444]</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3418181818181819</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1910253283041459</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.5588506945068098</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.367272727272728</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1000443458980044</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.1606635855846598</v>
+      </c>
+      <c r="O29" t="n">
+        <v>388</v>
+      </c>
+      <c r="P29" t="n">
+        <v>394</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>388</v>
+      </c>
+      <c r="R29" t="n">
+        <v>407</v>
+      </c>
+      <c r="S29" t="n">
+        <v>152.075715973184</v>
+      </c>
+      <c r="T29" t="n">
+        <v>136.3608687544823</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-15.71484721870172</v>
+      </c>
+      <c r="V29" t="n">
+        <v>135.1309322825701</v>
+      </c>
+      <c r="W29" t="n">
+        <v>151.5582926713905</v>
+      </c>
+      <c r="X29" t="n">
+        <v>17.81040842056274</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-107.8104652147293</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>109.2717120664063</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>61.07791439437866</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-86.70368065738676</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>106.0567766166083</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>66.79319925411019</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>66.36590310738995</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B-10_T-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>59.9670510708402</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>165</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ensemble_4signal</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[68, 91, 110, 135, 142]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[0.383543956043956, 0.31684065934065936, 0.41689560439560436, 0.11673076923076922]</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.3085027472527473</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1164326058594471</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.3774118930748362</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.234010989010989</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1167307692307692</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.2200233594273834</v>
+      </c>
+      <c r="O30" t="n">
+        <v>135</v>
+      </c>
+      <c r="P30" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>156</v>
+      </c>
+      <c r="R30" t="n">
+        <v>165</v>
+      </c>
+      <c r="S30" t="n">
+        <v>164.5848105238483</v>
+      </c>
+      <c r="T30" t="n">
+        <v>173.2075971332077</v>
+      </c>
+      <c r="U30" t="n">
+        <v>8.622786609359366</v>
+      </c>
+      <c r="V30" t="n">
+        <v>127.2152437317314</v>
+      </c>
+      <c r="W30" t="n">
+        <v>121.1783237639285</v>
+      </c>
+      <c r="X30" t="n">
+        <v>31.2205805668102</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-79.33778020818522</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>85.25965059329641</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>92.26951023504553</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-58.05214812250273</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>109.0124507597741</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>30.34550683638376</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>26.33732451688163</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_making/master.xlsx
+++ b/dataset_making/master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,15 +579,20 @@
           <t>wrist_speed_at_release_m_s</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>release_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.97095837366893</v>
+        <v>59.96430696014277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -600,88 +605,93 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>408</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[291, 316, 348, 401, 401]</t>
+          <t>[87, 118, 135, 143, 149]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.41686844229217107, 0.533591606133979, 0.8837610976594027, 0.0]</t>
+          <t>[0.5169742063492063, 0.28350198412698413, 0.13341269841269843, 0.1000595238095238]</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4585552865213882</v>
+        <v>0.2584871031746032</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3156109847838963</v>
+        <v>0.1644568571135626</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6882724811180981</v>
+        <v>0.6362284813972909</v>
       </c>
       <c r="K2" t="n">
-        <v>1.834221146085553</v>
+        <v>1.033948412698413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4335431799838579</v>
+        <v>0.1000595238095238</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3191826601565718</v>
+        <v>0.8622171134760422</v>
       </c>
       <c r="N2" t="n">
-        <v>375</v>
+        <v>143</v>
       </c>
       <c r="O2" t="n">
-        <v>401</v>
+        <v>149</v>
       </c>
       <c r="P2" t="n">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="Q2" t="n">
-        <v>408</v>
+        <v>149</v>
       </c>
       <c r="R2" t="n">
-        <v>170.5578369948597</v>
+        <v>139.015577024508</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>142.9280982007073</v>
+      </c>
+      <c r="V2" t="n">
+        <v>142.9280982007073</v>
+      </c>
       <c r="W2" t="n">
-        <v>-256.8290392545429</v>
+        <v>-562.4669483176417</v>
       </c>
       <c r="X2" t="n">
-        <v>-167.7548004341224</v>
+        <v>-237.3654033305984</v>
       </c>
       <c r="Y2" t="n">
-        <v>306.761843248315</v>
+        <v>610.5009440189739</v>
       </c>
       <c r="Z2" t="n">
-        <v>-194.2102282909209</v>
+        <v>-157.433501399148</v>
       </c>
       <c r="AA2" t="n">
-        <v>-156.8099907686192</v>
+        <v>-163.4324389536099</v>
       </c>
       <c r="AB2" t="n">
-        <v>249.6136734589394</v>
+        <v>226.9261321776779</v>
       </c>
       <c r="AC2" t="n">
-        <v>92.1884208810102</v>
+        <v>85.7056358273985</v>
       </c>
       <c r="AD2" t="n">
-        <v>28.1971264084378</v>
-      </c>
+        <v>38.80394992768173</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3051f922</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.96430696014277</v>
+        <v>60</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -694,83 +704,809 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[87, 118, 135, 143, 149]</t>
+          <t>[102, 125, 143, 185, 222]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.5169742063492063, 0.28350198412698413, 0.13341269841269843, 0.1000595238095238]</t>
+          <t>[0.38333333333333336, 0.3, 0.7, 0.6166666666666667]</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.2584871031746032</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1644568571135626</v>
+        <v>0.1637240225365708</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6362284813972909</v>
+        <v>0.3274480450731416</v>
       </c>
       <c r="K3" t="n">
-        <v>1.033948412698413</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1000595238095238</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8622171134760422</v>
+        <v>0.6542775424299568</v>
       </c>
       <c r="N3" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="O3" t="n">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="P3" t="n">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="Q3" t="n">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="R3" t="n">
-        <v>139.015577024508</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>159.9886405983499</v>
+      </c>
+      <c r="S3" t="n">
+        <v>165.9477119898054</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.95907139145541</v>
+      </c>
       <c r="U3" t="n">
-        <v>142.9280982007073</v>
+        <v>147.6960441740065</v>
       </c>
       <c r="V3" t="n">
-        <v>142.9280982007073</v>
+        <v>173.5375067144464</v>
       </c>
       <c r="W3" t="n">
-        <v>-562.4669483176417</v>
+        <v>-233.2376728852371</v>
       </c>
       <c r="X3" t="n">
-        <v>-237.3654033305984</v>
+        <v>-195.8683052262931</v>
       </c>
       <c r="Y3" t="n">
-        <v>610.5009440189739</v>
+        <v>304.5721672200879</v>
       </c>
       <c r="Z3" t="n">
-        <v>-157.433501399148</v>
+        <v>-157.154503670528</v>
       </c>
       <c r="AA3" t="n">
-        <v>-163.4324389536099</v>
+        <v>-178.741332149111</v>
       </c>
       <c r="AB3" t="n">
-        <v>226.9261321776779</v>
+        <v>238.0042055140388</v>
       </c>
       <c r="AC3" t="n">
-        <v>85.7056358273985</v>
+        <v>88.1173863413308</v>
       </c>
       <c r="AD3" t="n">
-        <v>38.80394992768173</v>
-      </c>
+        <v>88.1173863413308</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>324e1188</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[39, 60, 74, 104, 126]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09455671431591847</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2608461084577061</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9290980777877696</v>
+      </c>
+      <c r="N4" t="n">
+        <v>104</v>
+      </c>
+      <c r="O4" t="n">
+        <v>126</v>
+      </c>
+      <c r="P4" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>144</v>
+      </c>
+      <c r="R4" t="n">
+        <v>146.2370153336146</v>
+      </c>
+      <c r="S4" t="n">
+        <v>90.80948260711824</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-55.42753272649634</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>-176.5019353150292</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-161.3347266415383</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>239.1272196769968</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-232.3055980567109</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-169.8306428187528</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>287.764379534224</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>50.532376796942</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>50.532376796942</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5296fd61</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>172</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[66, 102, 115, 140, 159]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[0.6, 0.21666666666666667, 0.4166666666666667, 0.31666666666666665]</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1416053788997202</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3654332358702457</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.014399664938039</v>
+      </c>
+      <c r="N5" t="n">
+        <v>140</v>
+      </c>
+      <c r="O5" t="n">
+        <v>159</v>
+      </c>
+      <c r="P5" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>172</v>
+      </c>
+      <c r="R5" t="n">
+        <v>130.120654017213</v>
+      </c>
+      <c r="S5" t="n">
+        <v>170.9802080620529</v>
+      </c>
+      <c r="T5" t="n">
+        <v>40.85955404483991</v>
+      </c>
+      <c r="U5" t="n">
+        <v>153.169707840219</v>
+      </c>
+      <c r="V5" t="n">
+        <v>172.1998032540796</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-162.964036402209</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-205.9193725922683</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>262.6024850782908</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-131.3963083917026</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-180.9027141281654</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>223.5861843627735</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>66.28715163020401</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>66.28715163020401</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>68372319</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>188</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[83, 101, 118, 148, 172]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[0.3, 0.2833333333333333, 0.5, 0.4]</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08690272339422588</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2343444226361147</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.483333333333333</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.140319775390625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>148</v>
+      </c>
+      <c r="O6" t="n">
+        <v>172</v>
+      </c>
+      <c r="P6" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>188</v>
+      </c>
+      <c r="R6" t="n">
+        <v>148.6978025554788</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-167.1142939453125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-162.4537924804687</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>233.0631286414209</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-141.93495703125</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-156.7751451416015</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>211.4804439224417</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>91.81127061619543</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>91.81127061619543</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>93a73e01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[39, 60, 74, 104, 126]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09455671431591847</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2608461084577061</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.983334767607868</v>
+      </c>
+      <c r="N7" t="n">
+        <v>104</v>
+      </c>
+      <c r="O7" t="n">
+        <v>126</v>
+      </c>
+      <c r="P7" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>144</v>
+      </c>
+      <c r="R7" t="n">
+        <v>146.2370153336146</v>
+      </c>
+      <c r="S7" t="n">
+        <v>90.80948260711824</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-55.42753272649634</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>-186.8053477826579</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-170.7527436789885</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>253.0864228561108</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-245.8665847453006</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-179.7446143538577</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>304.5628077811456</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>53.48223635615436</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>53.48223635615436</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ravien</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>137</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[48, 64, 93, 113, 117]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[0.26666666666666666, 0.48333333333333334, 0.3333333333333333, 0.06666666666666667]</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1497103685268474</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5207317166151213</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3948693544708029</v>
+      </c>
+      <c r="N8" t="n">
+        <v>113</v>
+      </c>
+      <c r="O8" t="n">
+        <v>117</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>137</v>
+      </c>
+      <c r="R8" t="n">
+        <v>141.8835715327521</v>
+      </c>
+      <c r="S8" t="n">
+        <v>114.2584639841698</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-27.62510754858228</v>
+      </c>
+      <c r="U8" t="n">
+        <v>120.9587913280582</v>
+      </c>
+      <c r="V8" t="n">
+        <v>147.0618184763749</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-405.1679359959512</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-238.2634633397012</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>470.0324821986756</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-211.5529426608121</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-188.4309182004163</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>283.3034741797227</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>68.02571630402693</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>68.02571630402693</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ravien 2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[88, 108, 162, 163, 192]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[0.3333333333333333, 0.9, 0.016666666666666666, 0.48333333333333334]</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3177612660822937</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7332952294206776</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.733333333333334</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.069224948584209</v>
+      </c>
+      <c r="N9" t="n">
+        <v>163</v>
+      </c>
+      <c r="O9" t="n">
+        <v>192</v>
+      </c>
+      <c r="P9" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>200</v>
+      </c>
+      <c r="R9" t="n">
+        <v>135.3284782964824</v>
+      </c>
+      <c r="S9" t="n">
+        <v>148.9634442714724</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13.63496597498997</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>-170.7379109663018</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-161.0690270602319</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>234.722529211123</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-224.0349215487291</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-169.0981742556524</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>280.6881518873573</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>79.74137467015595</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>79.74137467015595</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>59.97095837366893</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>408</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[291, 316, 348, 401, 401]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0.41686844229217107, 0.533591606133979, 0.8837610976594027, 0.0]</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4585552865213882</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3156109847838963</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6882724811180981</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.834221146085553</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4335431799838579</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3191826601565718</v>
+      </c>
+      <c r="N10" t="n">
+        <v>375</v>
+      </c>
+      <c r="O10" t="n">
+        <v>401</v>
+      </c>
+      <c r="P10" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>408</v>
+      </c>
+      <c r="R10" t="n">
+        <v>170.5578369948597</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>-256.8290392545429</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-167.7548004341224</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>306.761843248315</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-194.2102282909209</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-156.8099907686192</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>249.6136734589394</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>92.1884208810102</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>28.1971264084378</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dataset_making/master.xlsx
+++ b/dataset_making/master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,11 +588,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>082cb73c</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.96430696014277</v>
+        <v>59.97403721332756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -605,93 +605,101 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[87, 118, 135, 143, 149]</t>
+          <t>[111, 136, 150, 173, 180]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.5169742063492063, 0.28350198412698413, 0.13341269841269843, 0.1000595238095238]</t>
+          <t>[0.41684704184704185, 0.23343434343434344, 0.3834992784992785, 0.11671717171717172]</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.2584871031746032</v>
+        <v>0.2876244588744589</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1644568571135626</v>
+        <v>0.1204536491799587</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6362284813972909</v>
+        <v>0.4187879210666634</v>
       </c>
       <c r="K2" t="n">
-        <v>1.033948412698413</v>
+        <v>1.150497835497835</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1000595238095238</v>
+        <v>0.1167171717171717</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8622171134760422</v>
+        <v>1.110456870865648</v>
       </c>
       <c r="N2" t="n">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="O2" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="Q2" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="R2" t="n">
-        <v>139.015577024508</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>143.1321177132381</v>
+      </c>
+      <c r="S2" t="n">
+        <v>174.4682420755044</v>
+      </c>
+      <c r="T2" t="n">
+        <v>31.33612436226625</v>
+      </c>
       <c r="U2" t="n">
-        <v>142.9280982007073</v>
+        <v>179.0763858142591</v>
       </c>
       <c r="V2" t="n">
-        <v>142.9280982007073</v>
+        <v>179.7459239566817</v>
       </c>
       <c r="W2" t="n">
-        <v>-562.4669483176417</v>
+        <v>-9.966930528626825</v>
       </c>
       <c r="X2" t="n">
-        <v>-237.3654033305984</v>
+        <v>-157.4462910227532</v>
       </c>
       <c r="Y2" t="n">
-        <v>610.5009440189739</v>
+        <v>157.7614473215303</v>
       </c>
       <c r="Z2" t="n">
-        <v>-157.433501399148</v>
+        <v>-41.44878079379559</v>
       </c>
       <c r="AA2" t="n">
-        <v>-163.4324389536099</v>
+        <v>-158.1921583857849</v>
       </c>
       <c r="AB2" t="n">
-        <v>226.9261321776779</v>
+        <v>163.5321387496824</v>
       </c>
       <c r="AC2" t="n">
-        <v>85.7056358273985</v>
+        <v>16.99424083800236</v>
       </c>
       <c r="AD2" t="n">
-        <v>38.80394992768173</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>16.99424083800236</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3051f922</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>59.96430696014277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -704,101 +712,93 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[102, 125, 143, 185, 222]</t>
+          <t>[87, 118, 135, 143, 149]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.38333333333333336, 0.3, 0.7, 0.6166666666666667]</t>
+          <t>[0.5169742063492063, 0.28350198412698413, 0.13341269841269843, 0.1000595238095238]</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.2584871031746032</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1637240225365708</v>
+        <v>0.1644568571135626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3274480450731416</v>
+        <v>0.6362284813972909</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1.033948412698413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.1000595238095238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6542775424299568</v>
+        <v>0.8622171134760422</v>
       </c>
       <c r="N3" t="n">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="O3" t="n">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="P3" t="n">
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="Q3" t="n">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="R3" t="n">
-        <v>159.9886405983499</v>
-      </c>
-      <c r="S3" t="n">
-        <v>165.9477119898054</v>
-      </c>
-      <c r="T3" t="n">
-        <v>5.95907139145541</v>
-      </c>
+        <v>139.015577024508</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>147.6960441740065</v>
+        <v>142.9280982007073</v>
       </c>
       <c r="V3" t="n">
-        <v>173.5375067144464</v>
+        <v>142.9280982007073</v>
       </c>
       <c r="W3" t="n">
-        <v>-233.2376728852371</v>
+        <v>-562.4669483176417</v>
       </c>
       <c r="X3" t="n">
-        <v>-195.8683052262931</v>
+        <v>-237.3654033305984</v>
       </c>
       <c r="Y3" t="n">
-        <v>304.5721672200879</v>
+        <v>610.5009440189739</v>
       </c>
       <c r="Z3" t="n">
-        <v>-157.154503670528</v>
+        <v>-157.433501399148</v>
       </c>
       <c r="AA3" t="n">
-        <v>-178.741332149111</v>
+        <v>-163.4324389536099</v>
       </c>
       <c r="AB3" t="n">
-        <v>238.0042055140388</v>
+        <v>226.9261321776779</v>
       </c>
       <c r="AC3" t="n">
-        <v>88.1173863413308</v>
+        <v>85.7056358273985</v>
       </c>
       <c r="AD3" t="n">
-        <v>88.1173863413308</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>wrist_speed_peak_drop</t>
-        </is>
-      </c>
+        <v>38.80394992768173</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>324e1188</t>
+          <t>263d664d</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>59.97403721332756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -811,82 +811,86 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[39, 60, 74, 104, 126]</t>
+          <t>[111, 136, 150, 173, 180]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
+          <t>[0.41684704184704185, 0.23343434343434344, 0.3834992784992785, 0.11671717171717172]</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3625</v>
+        <v>0.2876244588744589</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09455671431591847</v>
+        <v>0.1204536491799587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2608461084577061</v>
+        <v>0.4187879210666634</v>
       </c>
       <c r="K4" t="n">
-        <v>1.45</v>
+        <v>1.150497835497835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.1167171717171717</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9290980777877696</v>
+        <v>1.110456870865648</v>
       </c>
       <c r="N4" t="n">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="O4" t="n">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="P4" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="Q4" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>146.2370153336146</v>
+        <v>143.1321177132381</v>
       </c>
       <c r="S4" t="n">
-        <v>90.80948260711824</v>
+        <v>174.4682420755044</v>
       </c>
       <c r="T4" t="n">
-        <v>-55.42753272649634</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>31.33612436226625</v>
+      </c>
+      <c r="U4" t="n">
+        <v>179.0763858142591</v>
+      </c>
+      <c r="V4" t="n">
+        <v>179.7459239566817</v>
+      </c>
       <c r="W4" t="n">
-        <v>-176.5019353150292</v>
+        <v>-9.966930528626825</v>
       </c>
       <c r="X4" t="n">
-        <v>-161.3347266415383</v>
+        <v>-157.4462910227532</v>
       </c>
       <c r="Y4" t="n">
-        <v>239.1272196769968</v>
+        <v>157.7614473215303</v>
       </c>
       <c r="Z4" t="n">
-        <v>-232.3055980567109</v>
+        <v>-41.44878079379559</v>
       </c>
       <c r="AA4" t="n">
-        <v>-169.8306428187528</v>
+        <v>-158.1921583857849</v>
       </c>
       <c r="AB4" t="n">
-        <v>287.764379534224</v>
+        <v>163.5321387496824</v>
       </c>
       <c r="AC4" t="n">
-        <v>50.532376796942</v>
+        <v>16.99424083800236</v>
       </c>
       <c r="AD4" t="n">
-        <v>50.532376796942</v>
+        <v>16.99424083800236</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -897,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5296fd61</t>
+          <t>3051f922</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -914,86 +918,86 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[66, 102, 115, 140, 159]</t>
+          <t>[102, 125, 143, 185, 222]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0.6, 0.21666666666666667, 0.4166666666666667, 0.31666666666666665]</t>
+          <t>[0.38333333333333336, 0.3, 0.7, 0.6166666666666667]</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3875</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1416053788997202</v>
+        <v>0.1637240225365708</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3654332358702457</v>
+        <v>0.3274480450731416</v>
       </c>
       <c r="K5" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>1.014399664938039</v>
+        <v>0.6542775424299568</v>
       </c>
       <c r="N5" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="P5" t="n">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="Q5" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="R5" t="n">
-        <v>130.120654017213</v>
+        <v>159.9886405983499</v>
       </c>
       <c r="S5" t="n">
-        <v>170.9802080620529</v>
+        <v>165.9477119898054</v>
       </c>
       <c r="T5" t="n">
-        <v>40.85955404483991</v>
+        <v>5.95907139145541</v>
       </c>
       <c r="U5" t="n">
-        <v>153.169707840219</v>
+        <v>147.6960441740065</v>
       </c>
       <c r="V5" t="n">
-        <v>172.1998032540796</v>
+        <v>173.5375067144464</v>
       </c>
       <c r="W5" t="n">
-        <v>-162.964036402209</v>
+        <v>-233.2376728852371</v>
       </c>
       <c r="X5" t="n">
-        <v>-205.9193725922683</v>
+        <v>-195.8683052262931</v>
       </c>
       <c r="Y5" t="n">
-        <v>262.6024850782908</v>
+        <v>304.5721672200879</v>
       </c>
       <c r="Z5" t="n">
-        <v>-131.3963083917026</v>
+        <v>-157.154503670528</v>
       </c>
       <c r="AA5" t="n">
-        <v>-180.9027141281654</v>
+        <v>-178.741332149111</v>
       </c>
       <c r="AB5" t="n">
-        <v>223.5861843627735</v>
+        <v>238.0042055140388</v>
       </c>
       <c r="AC5" t="n">
-        <v>66.28715163020401</v>
+        <v>88.1173863413308</v>
       </c>
       <c r="AD5" t="n">
-        <v>66.28715163020401</v>
+        <v>88.1173863413308</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1004,7 +1008,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>68372319</t>
+          <t>324e1188</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1021,78 +1025,82 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[83, 101, 118, 148, 172]</t>
+          <t>[39, 60, 74, 104, 126]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0.3, 0.2833333333333333, 0.5, 0.4]</t>
+          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.3708333333333333</v>
+        <v>0.3625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08690272339422588</v>
+        <v>0.09455671431591847</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2343444226361147</v>
+        <v>0.2608461084577061</v>
       </c>
       <c r="K6" t="n">
-        <v>1.483333333333333</v>
+        <v>1.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M6" t="n">
-        <v>1.140319775390625</v>
+        <v>0.9290980777877696</v>
       </c>
       <c r="N6" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="O6" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="P6" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="Q6" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="R6" t="n">
-        <v>148.6978025554788</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>146.2370153336146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>90.80948260711824</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-55.42753272649634</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>-167.1142939453125</v>
+        <v>-176.5019353150292</v>
       </c>
       <c r="X6" t="n">
-        <v>-162.4537924804687</v>
+        <v>-161.3347266415383</v>
       </c>
       <c r="Y6" t="n">
-        <v>233.0631286414209</v>
+        <v>239.1272196769968</v>
       </c>
       <c r="Z6" t="n">
-        <v>-141.93495703125</v>
+        <v>-232.3055980567109</v>
       </c>
       <c r="AA6" t="n">
-        <v>-156.7751451416015</v>
+        <v>-169.8306428187528</v>
       </c>
       <c r="AB6" t="n">
-        <v>211.4804439224417</v>
+        <v>287.764379534224</v>
       </c>
       <c r="AC6" t="n">
-        <v>91.81127061619543</v>
+        <v>50.532376796942</v>
       </c>
       <c r="AD6" t="n">
-        <v>91.81127061619543</v>
+        <v>50.532376796942</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1103,7 +1111,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>93a73e01</t>
+          <t>5296fd61</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1120,82 +1128,86 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[39, 60, 74, 104, 126]</t>
+          <t>[66, 102, 115, 140, 159]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
+          <t>[0.6, 0.21666666666666667, 0.4166666666666667, 0.31666666666666665]</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3625</v>
+        <v>0.3875</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09455671431591847</v>
+        <v>0.1416053788997202</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2608461084577061</v>
+        <v>0.3654332358702457</v>
       </c>
       <c r="K7" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>0.983334767607868</v>
+        <v>1.014399664938039</v>
       </c>
       <c r="N7" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="O7" t="n">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="P7" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="Q7" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="R7" t="n">
-        <v>146.2370153336146</v>
+        <v>130.120654017213</v>
       </c>
       <c r="S7" t="n">
-        <v>90.80948260711824</v>
+        <v>170.9802080620529</v>
       </c>
       <c r="T7" t="n">
-        <v>-55.42753272649634</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+        <v>40.85955404483991</v>
+      </c>
+      <c r="U7" t="n">
+        <v>153.169707840219</v>
+      </c>
+      <c r="V7" t="n">
+        <v>172.1998032540796</v>
+      </c>
       <c r="W7" t="n">
-        <v>-186.8053477826579</v>
+        <v>-162.964036402209</v>
       </c>
       <c r="X7" t="n">
-        <v>-170.7527436789885</v>
+        <v>-205.9193725922683</v>
       </c>
       <c r="Y7" t="n">
-        <v>253.0864228561108</v>
+        <v>262.6024850782908</v>
       </c>
       <c r="Z7" t="n">
-        <v>-245.8665847453006</v>
+        <v>-131.3963083917026</v>
       </c>
       <c r="AA7" t="n">
-        <v>-179.7446143538577</v>
+        <v>-180.9027141281654</v>
       </c>
       <c r="AB7" t="n">
-        <v>304.5628077811456</v>
+        <v>223.5861843627735</v>
       </c>
       <c r="AC7" t="n">
-        <v>53.48223635615436</v>
+        <v>66.28715163020401</v>
       </c>
       <c r="AD7" t="n">
-        <v>53.48223635615436</v>
+        <v>66.28715163020401</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1206,7 +1218,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ravien</t>
+          <t>68372319</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1223,86 +1235,78 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[48, 64, 93, 113, 117]</t>
+          <t>[83, 101, 118, 148, 172]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[0.26666666666666666, 0.48333333333333334, 0.3333333333333333, 0.06666666666666667]</t>
+          <t>[0.3, 0.2833333333333333, 0.5, 0.4]</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2875</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1497103685268474</v>
+        <v>0.08690272339422588</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5207317166151213</v>
+        <v>0.2343444226361147</v>
       </c>
       <c r="K8" t="n">
-        <v>1.15</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3948693544708029</v>
+        <v>1.140319775390625</v>
       </c>
       <c r="N8" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="O8" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="R8" t="n">
-        <v>141.8835715327521</v>
-      </c>
-      <c r="S8" t="n">
-        <v>114.2584639841698</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-27.62510754858228</v>
-      </c>
-      <c r="U8" t="n">
-        <v>120.9587913280582</v>
-      </c>
-      <c r="V8" t="n">
-        <v>147.0618184763749</v>
-      </c>
+        <v>148.6978025554788</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>-405.1679359959512</v>
+        <v>-167.1142939453125</v>
       </c>
       <c r="X8" t="n">
-        <v>-238.2634633397012</v>
+        <v>-162.4537924804687</v>
       </c>
       <c r="Y8" t="n">
-        <v>470.0324821986756</v>
+        <v>233.0631286414209</v>
       </c>
       <c r="Z8" t="n">
-        <v>-211.5529426608121</v>
+        <v>-141.93495703125</v>
       </c>
       <c r="AA8" t="n">
-        <v>-188.4309182004163</v>
+        <v>-156.7751451416015</v>
       </c>
       <c r="AB8" t="n">
-        <v>283.3034741797227</v>
+        <v>211.4804439224417</v>
       </c>
       <c r="AC8" t="n">
-        <v>68.02571630402693</v>
+        <v>91.81127061619543</v>
       </c>
       <c r="AD8" t="n">
-        <v>68.02571630402693</v>
+        <v>91.81127061619543</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1313,7 +1317,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ravien 2</t>
+          <t>93a73e01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1330,82 +1334,82 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[88, 108, 162, 163, 192]</t>
+          <t>[39, 60, 74, 104, 126]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0.3333333333333333, 0.9, 0.016666666666666666, 0.48333333333333334]</t>
+          <t>[0.35, 0.23333333333333334, 0.5, 0.36666666666666664]</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3177612660822937</v>
+        <v>0.09455671431591847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7332952294206776</v>
+        <v>0.2608461084577061</v>
       </c>
       <c r="K9" t="n">
-        <v>1.733333333333334</v>
+        <v>1.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M9" t="n">
-        <v>1.069224948584209</v>
+        <v>0.983334767607868</v>
       </c>
       <c r="N9" t="n">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="O9" t="n">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="P9" t="n">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="Q9" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="R9" t="n">
-        <v>135.3284782964824</v>
+        <v>146.2370153336146</v>
       </c>
       <c r="S9" t="n">
-        <v>148.9634442714724</v>
+        <v>90.80948260711824</v>
       </c>
       <c r="T9" t="n">
-        <v>13.63496597498997</v>
+        <v>-55.42753272649634</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>-170.7379109663018</v>
+        <v>-186.8053477826579</v>
       </c>
       <c r="X9" t="n">
-        <v>-161.0690270602319</v>
+        <v>-170.7527436789885</v>
       </c>
       <c r="Y9" t="n">
-        <v>234.722529211123</v>
+        <v>253.0864228561108</v>
       </c>
       <c r="Z9" t="n">
-        <v>-224.0349215487291</v>
+        <v>-245.8665847453006</v>
       </c>
       <c r="AA9" t="n">
-        <v>-169.0981742556524</v>
+        <v>-179.7446143538577</v>
       </c>
       <c r="AB9" t="n">
-        <v>280.6881518873573</v>
+        <v>304.5628077811456</v>
       </c>
       <c r="AC9" t="n">
-        <v>79.74137467015595</v>
+        <v>53.48223635615436</v>
       </c>
       <c r="AD9" t="n">
-        <v>79.74137467015595</v>
+        <v>53.48223635615436</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1416,97 +1420,414 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Ravien</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>137</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[48, 64, 93, 113, 117]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0.26666666666666666, 0.48333333333333334, 0.3333333333333333, 0.06666666666666667]</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1497103685268474</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5207317166151213</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3948693544708029</v>
+      </c>
+      <c r="N10" t="n">
+        <v>113</v>
+      </c>
+      <c r="O10" t="n">
+        <v>117</v>
+      </c>
+      <c r="P10" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>137</v>
+      </c>
+      <c r="R10" t="n">
+        <v>141.8835715327521</v>
+      </c>
+      <c r="S10" t="n">
+        <v>114.2584639841698</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-27.62510754858228</v>
+      </c>
+      <c r="U10" t="n">
+        <v>120.9587913280582</v>
+      </c>
+      <c r="V10" t="n">
+        <v>147.0618184763749</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-405.1679359959512</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-238.2634633397012</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>470.0324821986756</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-211.5529426608121</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-188.4309182004163</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>283.3034741797227</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>68.02571630402693</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>68.02571630402693</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ravien 2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[88, 108, 162, 163, 192]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0.3333333333333333, 0.9, 0.016666666666666666, 0.48333333333333334]</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3177612660822937</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7332952294206776</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.733333333333334</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.069224948584209</v>
+      </c>
+      <c r="N11" t="n">
+        <v>163</v>
+      </c>
+      <c r="O11" t="n">
+        <v>192</v>
+      </c>
+      <c r="P11" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>135.3284782964824</v>
+      </c>
+      <c r="S11" t="n">
+        <v>148.9634442714724</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13.63496597498997</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>-170.7379109663018</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-161.0690270602319</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>234.722529211123</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-224.0349215487291</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-169.0981742556524</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>280.6881518873573</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>79.74137467015595</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>79.74137467015595</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bf8e1b84</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>59.97425997425997</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>172</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[105, 130, 138, 162, 171]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0.4168454935622318, 0.13339055793991417, 0.4001716738197425, 0.15006437768240344]</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.275118025751073</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1336508324468009</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4857945315721636</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.100472103004292</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1500643776824034</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.261473293661484</v>
+      </c>
+      <c r="N12" t="n">
+        <v>162</v>
+      </c>
+      <c r="O12" t="n">
+        <v>171</v>
+      </c>
+      <c r="P12" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>172</v>
+      </c>
+      <c r="R12" t="n">
+        <v>106.9332100397187</v>
+      </c>
+      <c r="S12" t="n">
+        <v>177.5277786304321</v>
+      </c>
+      <c r="T12" t="n">
+        <v>70.59456859071338</v>
+      </c>
+      <c r="U12" t="n">
+        <v>140.1394383312312</v>
+      </c>
+      <c r="V12" t="n">
+        <v>140.1394383312312</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-12.65540118438271</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-159.86244831555</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>160.3625940192399</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-44.65410373932032</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-160.7505249294037</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>166.8374066144665</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17.9236373082372</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.9236373082372</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>new</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>59.97095837366893</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>SIDE</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>408</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[291, 316, 348, 401, 401]</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>[0.41686844229217107, 0.533591606133979, 0.8837610976594027, 0.0]</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>0.4585552865213882</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>0.3156109847838963</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>0.6882724811180981</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>1.834221146085553</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>0.4335431799838579</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M13" t="n">
         <v>0.3191826601565718</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>375</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O13" t="n">
         <v>401</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P13" t="n">
         <v>401</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q13" t="n">
         <v>408</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>170.5578369948597</v>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>-256.8290392545429</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X13" t="n">
         <v>-167.7548004341224</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y13" t="n">
         <v>306.761843248315</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z13" t="n">
         <v>-194.2102282909209</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA13" t="n">
         <v>-156.8099907686192</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB13" t="n">
         <v>249.6136734589394</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC13" t="n">
         <v>92.1884208810102</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD13" t="n">
         <v>28.1971264084378</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dataset_making/master.xlsx
+++ b/dataset_making/master.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,161 +413,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>trial_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bowling_arm</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>view_mode</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>release_frame</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>last5_steps_frame</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>last5_step_intervals_s</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>step_duration_mean_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>step_duration_std_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>step_duration_cv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>final5_total_duration_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>stride_duration_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>stride_length_m</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>bfc_frame</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ffc_frame</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>arm_back_frame</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>release_frame.1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>elbow_angle_arm_back_deg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>elbow_angle_release_deg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>elbow_extension_deg</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>knee_angle_ffc_deg</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>knee_angle_release_deg</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>head_dx_ffc_cm</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>head_dy_ffc_cm</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>head_d_ffc_cm</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>head_dx_bfc_cm</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>head_dy_bfc_cm</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>head_d_bfc_cm</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>peak_wrist_speed_m_s</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>wrist_speed_at_release_m_s</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>release_method</t>
         </is>
@@ -1829,6 +1817,113 @@
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SIDE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>310</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[229, 242, 265, 304, 310]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0.21666666666666667, 0.38333333333333336, 0.65, 0.1]</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.206617937803624</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6122012971959229</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7190320095486111</v>
+      </c>
+      <c r="N14" t="n">
+        <v>304</v>
+      </c>
+      <c r="O14" t="n">
+        <v>310</v>
+      </c>
+      <c r="P14" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>310</v>
+      </c>
+      <c r="R14" t="n">
+        <v>69.27219899461528</v>
+      </c>
+      <c r="S14" t="n">
+        <v>52.59366242929705</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-16.67853656531823</v>
+      </c>
+      <c r="U14" t="n">
+        <v>168.9307053738884</v>
+      </c>
+      <c r="V14" t="n">
+        <v>168.9307053738884</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-441.2480281032986</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-266.8268267415365</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>515.6514111044469</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-416.4116744791666</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-273.2405856662326</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>498.0553185116782</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>83.98831370592275</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>83.98831370592275</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>wrist_speed_peak_drop</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
